--- a/data/Formula_1/Formula_1.xlsx
+++ b/data/Formula_1/Formula_1.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vyan\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vyan\Documents\GitHub\Formula_1\data\Formula_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D60A70-3732-4C4C-9D4F-6073BC70A67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF2CF6C-860C-47AA-8587-92CB5E7B2540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Drivers" sheetId="1" r:id="rId1"/>
     <sheet name="Track_Details" sheetId="2" r:id="rId2"/>
     <sheet name="Track_Log" sheetId="3" r:id="rId3"/>
-    <sheet name="Constructor" sheetId="4" r:id="rId4"/>
-    <sheet name="Times" sheetId="7" r:id="rId5"/>
-    <sheet name="Constructor_Log" sheetId="5" r:id="rId6"/>
+    <sheet name="Times" sheetId="7" r:id="rId4"/>
+    <sheet name="Constructor_Log" sheetId="5" r:id="rId5"/>
+    <sheet name="Constructor" sheetId="4" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="325">
   <si>
     <t>Name</t>
   </si>
@@ -542,13 +545,487 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>Now your table is fully detailed! Let me know if you need any tweaks.</t>
+  </si>
+  <si>
+    <t>1:16.315</t>
+  </si>
+  <si>
+    <t>1:32.575</t>
+  </si>
+  <si>
+    <t>1:28.877</t>
+  </si>
+  <si>
+    <t>1:31.414</t>
+  </si>
+  <si>
+    <t>1:28.739</t>
+  </si>
+  <si>
+    <t>1:29.171</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1:16.328</t>
+  </si>
+  <si>
+    <t>1:32.640</t>
+  </si>
+  <si>
+    <t>1:28.186</t>
+  </si>
+  <si>
+    <t>1:31.462</t>
+  </si>
+  <si>
+    <t>1:28.421</t>
+  </si>
+  <si>
+    <t>1:28.345</t>
+  </si>
+  <si>
+    <t>1:15.937</t>
+  </si>
+  <si>
+    <t>1:11.994</t>
+  </si>
+  <si>
+    <t>1:16.288</t>
+  </si>
+  <si>
+    <t>1:32.121</t>
+  </si>
+  <si>
+    <t>1:28.337</t>
+  </si>
+  <si>
+    <t>1:31.634</t>
+  </si>
+  <si>
+    <t>1:28.548</t>
+  </si>
+  <si>
+    <t>1:28.455</t>
+  </si>
+  <si>
+    <t>1:15.695</t>
+  </si>
+  <si>
+    <t>1:11.674</t>
+  </si>
+  <si>
+    <t>1:16.369</t>
+  </si>
+  <si>
+    <t>1:32.327</t>
+  </si>
+  <si>
+    <t>1:29.271</t>
+  </si>
+  <si>
+    <t>1:32.283</t>
+  </si>
+  <si>
+    <t>1:28.645</t>
+  </si>
+  <si>
+    <t>1:29.028</t>
+  </si>
+  <si>
+    <t>1:15.817</t>
+  </si>
+  <si>
+    <t>1:12.563</t>
+  </si>
+  <si>
+    <t>1:16.029</t>
+  </si>
+  <si>
+    <t>1:31.518</t>
+  </si>
+  <si>
+    <t>1:27.920</t>
+  </si>
+  <si>
+    <t>1:31.454</t>
+  </si>
+  <si>
+    <t>1:28.552</t>
+  </si>
+  <si>
+    <t>1:28.325</t>
+  </si>
+  <si>
+    <t>1:16.108</t>
+  </si>
+  <si>
+    <t>1:11.229</t>
+  </si>
+  <si>
+    <t>1:16.213</t>
+  </si>
+  <si>
+    <t>1:31.212</t>
+  </si>
+  <si>
+    <t>1:27.942</t>
+  </si>
+  <si>
+    <t>1:31.219</t>
+  </si>
+  <si>
+    <t>1:28.372</t>
+  </si>
+  <si>
+    <t>1:28.231</t>
+  </si>
+  <si>
+    <t>1:16.163</t>
+  </si>
+  <si>
+    <t>1:11.575</t>
+  </si>
+  <si>
+    <t>1:17.174</t>
+  </si>
+  <si>
+    <t>1:32.651</t>
+  </si>
+  <si>
+    <t>1:28.696</t>
+  </si>
+  <si>
+    <t>1:31.594</t>
+  </si>
+  <si>
+    <t>1:29.092</t>
+  </si>
+  <si>
+    <t>1:28.303</t>
+  </si>
+  <si>
+    <t>1:16.613</t>
+  </si>
+  <si>
+    <t>1:11.839</t>
+  </si>
+  <si>
+    <t>No time</t>
+  </si>
+  <si>
+    <t>1:32.269</t>
+  </si>
+  <si>
+    <t>1:28.228</t>
+  </si>
+  <si>
+    <t>1:32.373</t>
+  </si>
+  <si>
+    <t>1:28.536</t>
+  </si>
+  <si>
+    <t>1:29.825</t>
+  </si>
+  <si>
+    <t>1:16.918</t>
+  </si>
+  <si>
+    <t>1:11.979</t>
+  </si>
+  <si>
+    <t>1:16.516</t>
+  </si>
+  <si>
+    <t>1:32.539</t>
+  </si>
+  <si>
+    <t>1:28.622</t>
+  </si>
+  <si>
+    <t>1:32.186</t>
+  </si>
+  <si>
+    <t>1:29.462</t>
+  </si>
+  <si>
+    <t>1:29.312</t>
+  </si>
+  <si>
+    <t>1:16.340</t>
+  </si>
+  <si>
+    <t>1:11.902</t>
+  </si>
+  <si>
+    <t>1:16.579</t>
+  </si>
+  <si>
+    <t>1:32.675</t>
+  </si>
+  <si>
+    <t>1:28.570</t>
+  </si>
+  <si>
+    <t>1:32.067</t>
+  </si>
+  <si>
+    <t>1:28.782</t>
+  </si>
+  <si>
+    <t>1:28.542</t>
+  </si>
+  <si>
+    <t>1:16.518</t>
+  </si>
+  <si>
+    <t>1:11.871</t>
+  </si>
+  <si>
+    <t>1:15.912</t>
+  </si>
+  <si>
+    <t>1:31.396</t>
+  </si>
+  <si>
+    <t>1:27.845</t>
+  </si>
+  <si>
+    <t>1:31.107</t>
+  </si>
+  <si>
+    <t>1:27.805</t>
+  </si>
+  <si>
+    <t>1:27.890</t>
+  </si>
+  <si>
+    <t>1:15.894</t>
+  </si>
+  <si>
+    <t>1:11.285</t>
+  </si>
+  <si>
+    <t>1:16.062</t>
+  </si>
+  <si>
+    <t>1:31.723</t>
+  </si>
+  <si>
+    <t>1:27.687</t>
+  </si>
+  <si>
+    <t>1:31.392</t>
+  </si>
+  <si>
+    <t>1:27.901</t>
+  </si>
+  <si>
+    <t>1:27.951</t>
+  </si>
+  <si>
+    <t>1:15.500</t>
+  </si>
+  <si>
+    <t>1:11.308</t>
+  </si>
+  <si>
+    <t>1:16.525</t>
+  </si>
+  <si>
+    <t>1:31.999</t>
+  </si>
+  <si>
+    <t>1:27.968</t>
+  </si>
+  <si>
+    <t>1:31.415</t>
+  </si>
+  <si>
+    <t>1:28.128</t>
+  </si>
+  <si>
+    <t>1:27.858</t>
+  </si>
+  <si>
+    <t>1:15.943</t>
+  </si>
+  <si>
+    <t>1:11.880</t>
+  </si>
+  <si>
+    <t>1:15.971</t>
+  </si>
+  <si>
+    <t>1:31.952</t>
+  </si>
+  <si>
+    <t>1:27.843</t>
+  </si>
+  <si>
+    <t>1:31.494</t>
+  </si>
+  <si>
+    <t>1:28.282</t>
+  </si>
+  <si>
+    <t>1:27.688</t>
+  </si>
+  <si>
+    <t>1:15.852</t>
+  </si>
+  <si>
+    <t>1:11.507</t>
+  </si>
+  <si>
+    <t>1:16.354</t>
+  </si>
+  <si>
+    <t>1:32.171</t>
+  </si>
+  <si>
+    <t>1:28.278</t>
+  </si>
+  <si>
+    <t>1:31.591</t>
+  </si>
+  <si>
+    <t>1:28.571</t>
+  </si>
+  <si>
+    <t>1:28.394</t>
+  </si>
+  <si>
+    <t>1:16.253</t>
+  </si>
+  <si>
+    <t>1:11.811</t>
+  </si>
+  <si>
+    <t>1:16.225</t>
+  </si>
+  <si>
+    <t>1:32.316</t>
+  </si>
+  <si>
+    <t>1:27.967</t>
+  </si>
+  <si>
+    <t>1:31.751</t>
+  </si>
+  <si>
+    <t>1:28.226</t>
+  </si>
+  <si>
+    <t>1:29.246</t>
+  </si>
+  <si>
+    <t>1:11.800</t>
+  </si>
+  <si>
+    <t>1:16.018</t>
+  </si>
+  <si>
+    <t>1:31.916</t>
+  </si>
+  <si>
+    <t>1:27.943</t>
+  </si>
+  <si>
+    <t>1:31.303</t>
+  </si>
+  <si>
+    <t>1:27.778</t>
+  </si>
+  <si>
+    <t>1:27.953</t>
+  </si>
+  <si>
+    <t>1:15.175</t>
+  </si>
+  <si>
+    <t>1:11.431</t>
+  </si>
+  <si>
+    <t>1:17.094</t>
+  </si>
+  <si>
+    <t>1:32.729</t>
+  </si>
+  <si>
+    <t>1:28.554</t>
+  </si>
+  <si>
+    <t>1:32.165</t>
+  </si>
+  <si>
+    <t>1:28.561</t>
+  </si>
+  <si>
+    <t>1:28.914</t>
+  </si>
+  <si>
+    <t>1:16.379</t>
+  </si>
+  <si>
+    <t>1:11.818</t>
+  </si>
+  <si>
+    <t>1:16.245</t>
+  </si>
+  <si>
+    <t>1:32.462</t>
+  </si>
+  <si>
+    <t>1:28.218</t>
+  </si>
+  <si>
+    <t>1:32.040</t>
+  </si>
+  <si>
+    <t>1:28.279</t>
+  </si>
+  <si>
+    <t>1:27.859</t>
+  </si>
+  <si>
+    <t>1:16.123</t>
+  </si>
+  <si>
+    <t>1:11.629</t>
+  </si>
+  <si>
+    <t>1:16.360</t>
+  </si>
+  <si>
+    <t>1:32.457</t>
+  </si>
+  <si>
+    <t>1:28.209</t>
+  </si>
+  <si>
+    <t>1:28.354</t>
+  </si>
+  <si>
+    <t>1:27.899</t>
+  </si>
+  <si>
+    <t>1:15.987</t>
+  </si>
+  <si>
+    <t>1:11.707</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,6 +1072,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -631,7 +1115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -682,11 +1166,37 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="47" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="109">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2051,22 +2561,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2174,6 +2668,1585 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="qualifying"/>
+      <sheetName val="Australian_Grand_Prix"/>
+      <sheetName val="Chinese_Grand_Prix"/>
+      <sheetName val="Japanese_Grand_Prix"/>
+      <sheetName val="Bahrain_Grand_Prix"/>
+      <sheetName val="Saudi_Arabian_Grand_Prix"/>
+      <sheetName val="Miami_Grand_Prix"/>
+      <sheetName val="Emilia_Romagna_Grand_Prix"/>
+      <sheetName val="Monaco_Grand_Prix"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="24">
+          <cell r="J24" t="str">
+            <v>1</v>
+          </cell>
+          <cell r="L24" t="str">
+            <v>Lando Norris</v>
+          </cell>
+          <cell r="P24" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="J25" t="str">
+            <v>2</v>
+          </cell>
+          <cell r="L25" t="str">
+            <v>Max Verstappen</v>
+          </cell>
+          <cell r="P25" t="str">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26" t="str">
+            <v>3</v>
+          </cell>
+          <cell r="L26" t="str">
+            <v>George Russell</v>
+          </cell>
+          <cell r="P26" t="str">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="J27" t="str">
+            <v>4</v>
+          </cell>
+          <cell r="L27" t="str">
+            <v>Andrea Kimi Antonelli</v>
+          </cell>
+          <cell r="P27" t="str">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="J28" t="str">
+            <v>5</v>
+          </cell>
+          <cell r="L28" t="str">
+            <v>Alexander Albon</v>
+          </cell>
+          <cell r="P28" t="str">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="J29" t="str">
+            <v>6</v>
+          </cell>
+          <cell r="L29" t="str">
+            <v>Lance Stroll</v>
+          </cell>
+          <cell r="P29" t="str">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="J30" t="str">
+            <v>7</v>
+          </cell>
+          <cell r="L30" t="str">
+            <v>Nico Hülkenberg</v>
+          </cell>
+          <cell r="P30" t="str">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31" t="str">
+            <v>8</v>
+          </cell>
+          <cell r="L31" t="str">
+            <v>Charles Leclerc</v>
+          </cell>
+          <cell r="P31" t="str">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="J32" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="L32" t="str">
+            <v>Oscar Piastri</v>
+          </cell>
+          <cell r="P32" t="str">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="J33" t="str">
+            <v>10</v>
+          </cell>
+          <cell r="L33" t="str">
+            <v>Lewis Hamilton</v>
+          </cell>
+          <cell r="P33" t="str">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="J34" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="L34" t="str">
+            <v>Pierre Gasly</v>
+          </cell>
+          <cell r="P34" t="str">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="J35" t="str">
+            <v>12</v>
+          </cell>
+          <cell r="L35" t="str">
+            <v>Yuki Tsunoda</v>
+          </cell>
+          <cell r="P35" t="str">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="J36" t="str">
+            <v>13</v>
+          </cell>
+          <cell r="L36" t="str">
+            <v>Esteban Ocon</v>
+          </cell>
+          <cell r="P36" t="str">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="L37" t="str">
+            <v>Oliver Bearman</v>
+          </cell>
+          <cell r="P37" t="str">
+            <v>PL</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="J38" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L38" t="str">
+            <v>Liam Lawson</v>
+          </cell>
+          <cell r="P38" t="str">
+            <v>PL</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="J39" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L39" t="str">
+            <v>Gabriel Bortoleto</v>
+          </cell>
+          <cell r="P39" t="str">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="J40" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L40" t="str">
+            <v>Fernando Alonso</v>
+          </cell>
+          <cell r="P40" t="str">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="J41" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L41" t="str">
+            <v>Carlos Sainz Jr.</v>
+          </cell>
+          <cell r="P41" t="str">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="J42" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L42" t="str">
+            <v>Jack Doohan</v>
+          </cell>
+          <cell r="P42" t="str">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="J43" t="str">
+            <v>DNS1</v>
+          </cell>
+          <cell r="L43" t="str">
+            <v>Isack Hadjar</v>
+          </cell>
+          <cell r="P43" t="str">
+            <v>—1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="24">
+          <cell r="J24" t="str">
+            <v>1</v>
+          </cell>
+          <cell r="L24" t="str">
+            <v>Lewis Hamilton</v>
+          </cell>
+          <cell r="P24" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="J25" t="str">
+            <v>2</v>
+          </cell>
+          <cell r="L25" t="str">
+            <v>Oscar Piastri</v>
+          </cell>
+          <cell r="P25" t="str">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26" t="str">
+            <v>3</v>
+          </cell>
+          <cell r="L26" t="str">
+            <v>Max Verstappen</v>
+          </cell>
+          <cell r="P26" t="str">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="J27" t="str">
+            <v>4</v>
+          </cell>
+          <cell r="L27" t="str">
+            <v>George Russell</v>
+          </cell>
+          <cell r="P27" t="str">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="J28" t="str">
+            <v>5</v>
+          </cell>
+          <cell r="L28" t="str">
+            <v>Charles Leclerc</v>
+          </cell>
+          <cell r="P28" t="str">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="J29" t="str">
+            <v>6</v>
+          </cell>
+          <cell r="L29" t="str">
+            <v>Yuki Tsunoda</v>
+          </cell>
+          <cell r="P29" t="str">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="J30" t="str">
+            <v>7</v>
+          </cell>
+          <cell r="L30" t="str">
+            <v>Andrea Kimi Antonelli</v>
+          </cell>
+          <cell r="P30" t="str">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31" t="str">
+            <v>8</v>
+          </cell>
+          <cell r="L31" t="str">
+            <v>Lando Norris</v>
+          </cell>
+          <cell r="P31" t="str">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="J32" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="L32" t="str">
+            <v>Lance Stroll</v>
+          </cell>
+          <cell r="P32" t="str">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="J33" t="str">
+            <v>10</v>
+          </cell>
+          <cell r="L33" t="str">
+            <v>Fernando Alonso</v>
+          </cell>
+          <cell r="P33" t="str">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="J34" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="L34" t="str">
+            <v>Alexander Albon</v>
+          </cell>
+          <cell r="P34" t="str">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="J35" t="str">
+            <v>12</v>
+          </cell>
+          <cell r="L35" t="str">
+            <v>Pierre Gasly</v>
+          </cell>
+          <cell r="P35" t="str">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="J36" t="str">
+            <v>13</v>
+          </cell>
+          <cell r="L36" t="str">
+            <v>Isack Hadjar</v>
+          </cell>
+          <cell r="P36" t="str">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="L37" t="str">
+            <v>Liam Lawson</v>
+          </cell>
+          <cell r="P37" t="str">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="J38" t="str">
+            <v>15</v>
+          </cell>
+          <cell r="L38" t="str">
+            <v>Oliver Bearman</v>
+          </cell>
+          <cell r="P38" t="str">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="J39" t="str">
+            <v>16</v>
+          </cell>
+          <cell r="L39" t="str">
+            <v>Esteban Ocon</v>
+          </cell>
+          <cell r="P39" t="str">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="J40" t="str">
+            <v>17</v>
+          </cell>
+          <cell r="L40" t="str">
+            <v>Carlos Sainz Jr.</v>
+          </cell>
+          <cell r="P40" t="str">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="J41" t="str">
+            <v>18</v>
+          </cell>
+          <cell r="L41" t="str">
+            <v>Gabriel Bortoleto</v>
+          </cell>
+          <cell r="P41" t="str">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="J42" t="str">
+            <v>19</v>
+          </cell>
+          <cell r="L42" t="str">
+            <v>Nico Hülkenberg</v>
+          </cell>
+          <cell r="P42" t="str">
+            <v>PL</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="J43" t="str">
+            <v>20</v>
+          </cell>
+          <cell r="L43" t="str">
+            <v>Jack Doohan</v>
+          </cell>
+          <cell r="P43" t="str">
+            <v>16</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="24">
+          <cell r="J24" t="str">
+            <v>1</v>
+          </cell>
+          <cell r="L24" t="str">
+            <v>Max Verstappen</v>
+          </cell>
+          <cell r="P24" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="J25" t="str">
+            <v>2</v>
+          </cell>
+          <cell r="L25" t="str">
+            <v>Lando Norris</v>
+          </cell>
+          <cell r="P25" t="str">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26" t="str">
+            <v>3</v>
+          </cell>
+          <cell r="L26" t="str">
+            <v>Oscar Piastri</v>
+          </cell>
+          <cell r="P26" t="str">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="J27" t="str">
+            <v>4</v>
+          </cell>
+          <cell r="L27" t="str">
+            <v>Charles Leclerc</v>
+          </cell>
+          <cell r="P27" t="str">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="J28" t="str">
+            <v>5</v>
+          </cell>
+          <cell r="L28" t="str">
+            <v>George Russell</v>
+          </cell>
+          <cell r="P28" t="str">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="J29" t="str">
+            <v>6</v>
+          </cell>
+          <cell r="L29" t="str">
+            <v>Andrea Kimi Antonelli</v>
+          </cell>
+          <cell r="P29" t="str">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="J30" t="str">
+            <v>7</v>
+          </cell>
+          <cell r="L30" t="str">
+            <v>Lewis Hamilton</v>
+          </cell>
+          <cell r="P30" t="str">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31" t="str">
+            <v>8</v>
+          </cell>
+          <cell r="L31" t="str">
+            <v>Isack Hadjar</v>
+          </cell>
+          <cell r="P31" t="str">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="J32" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="L32" t="str">
+            <v>Alexander Albon</v>
+          </cell>
+          <cell r="P32" t="str">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="J33" t="str">
+            <v>10</v>
+          </cell>
+          <cell r="L33" t="str">
+            <v>Oliver Bearman</v>
+          </cell>
+          <cell r="P33" t="str">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="J34" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="L34" t="str">
+            <v>Fernando Alonso</v>
+          </cell>
+          <cell r="P34" t="str">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="J35" t="str">
+            <v>12</v>
+          </cell>
+          <cell r="L35" t="str">
+            <v>Yuki Tsunoda</v>
+          </cell>
+          <cell r="P35" t="str">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="J36" t="str">
+            <v>13</v>
+          </cell>
+          <cell r="L36" t="str">
+            <v>Pierre Gasly</v>
+          </cell>
+          <cell r="P36" t="str">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="L37" t="str">
+            <v>Carlos Sainz Jr.</v>
+          </cell>
+          <cell r="P37" t="str">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="J38" t="str">
+            <v>15</v>
+          </cell>
+          <cell r="L38" t="str">
+            <v>Jack Doohan</v>
+          </cell>
+          <cell r="P38" t="str">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="J39" t="str">
+            <v>16</v>
+          </cell>
+          <cell r="L39" t="str">
+            <v>Nico Hülkenberg</v>
+          </cell>
+          <cell r="P39" t="str">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="J40" t="str">
+            <v>17</v>
+          </cell>
+          <cell r="L40" t="str">
+            <v>Liam Lawson</v>
+          </cell>
+          <cell r="P40" t="str">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="J41" t="str">
+            <v>18</v>
+          </cell>
+          <cell r="L41" t="str">
+            <v>Esteban Ocon</v>
+          </cell>
+          <cell r="P41" t="str">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="J42" t="str">
+            <v>19</v>
+          </cell>
+          <cell r="L42" t="str">
+            <v>Gabriel Bortoleto</v>
+          </cell>
+          <cell r="P42" t="str">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="J43" t="str">
+            <v>20</v>
+          </cell>
+          <cell r="L43" t="str">
+            <v>Lance Stroll</v>
+          </cell>
+          <cell r="P43" t="str">
+            <v>20</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="24">
+          <cell r="J24" t="str">
+            <v>1</v>
+          </cell>
+          <cell r="L24" t="str">
+            <v>Oscar Piastri</v>
+          </cell>
+          <cell r="P24" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="J25" t="str">
+            <v>2</v>
+          </cell>
+          <cell r="L25" t="str">
+            <v>George Russell</v>
+          </cell>
+          <cell r="P25" t="str">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26" t="str">
+            <v>3</v>
+          </cell>
+          <cell r="L26" t="str">
+            <v>Lando Norris</v>
+          </cell>
+          <cell r="P26" t="str">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="J27" t="str">
+            <v>4</v>
+          </cell>
+          <cell r="L27" t="str">
+            <v>Charles Leclerc</v>
+          </cell>
+          <cell r="P27" t="str">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="J28" t="str">
+            <v>5</v>
+          </cell>
+          <cell r="L28" t="str">
+            <v>Lewis Hamilton</v>
+          </cell>
+          <cell r="P28" t="str">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="J29" t="str">
+            <v>6</v>
+          </cell>
+          <cell r="L29" t="str">
+            <v>Max Verstappen</v>
+          </cell>
+          <cell r="P29" t="str">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="J30" t="str">
+            <v>7</v>
+          </cell>
+          <cell r="L30" t="str">
+            <v>Pierre Gasly</v>
+          </cell>
+          <cell r="P30" t="str">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31" t="str">
+            <v>8</v>
+          </cell>
+          <cell r="L31" t="str">
+            <v>Esteban Ocon</v>
+          </cell>
+          <cell r="P31" t="str">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="J32" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="L32" t="str">
+            <v>Yuki Tsunoda</v>
+          </cell>
+          <cell r="P32" t="str">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="J33" t="str">
+            <v>10</v>
+          </cell>
+          <cell r="L33" t="str">
+            <v>Oliver Bearman</v>
+          </cell>
+          <cell r="P33" t="str">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="J34" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="L34" t="str">
+            <v>Andrea Kimi Antonelli</v>
+          </cell>
+          <cell r="P34" t="str">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="J35" t="str">
+            <v>12</v>
+          </cell>
+          <cell r="L35" t="str">
+            <v>Alexander Albon</v>
+          </cell>
+          <cell r="P35" t="str">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="J36" t="str">
+            <v>13</v>
+          </cell>
+          <cell r="L36" t="str">
+            <v>Isack Hadjar</v>
+          </cell>
+          <cell r="P36" t="str">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="L37" t="str">
+            <v>Jack Doohan</v>
+          </cell>
+          <cell r="P37" t="str">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="J38" t="str">
+            <v>15</v>
+          </cell>
+          <cell r="L38" t="str">
+            <v>Fernando Alonso</v>
+          </cell>
+          <cell r="P38" t="str">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="J39" t="str">
+            <v>16</v>
+          </cell>
+          <cell r="L39" t="str">
+            <v>Liam Lawson</v>
+          </cell>
+          <cell r="P39" t="str">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="J40" t="str">
+            <v>17</v>
+          </cell>
+          <cell r="L40" t="str">
+            <v>Lance Stroll</v>
+          </cell>
+          <cell r="P40" t="str">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="J41" t="str">
+            <v>18</v>
+          </cell>
+          <cell r="L41" t="str">
+            <v>Gabriel Bortoleto</v>
+          </cell>
+          <cell r="P41" t="str">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="J42" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L42" t="str">
+            <v>Carlos Sainz Jr.</v>
+          </cell>
+          <cell r="P42" t="str">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="J43" t="str">
+            <v>DSQ</v>
+          </cell>
+          <cell r="L43" t="str">
+            <v>Nico Hülkenberg</v>
+          </cell>
+          <cell r="P43" t="str">
+            <v>16</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5">
+        <row r="24">
+          <cell r="J24" t="str">
+            <v>1</v>
+          </cell>
+          <cell r="L24" t="str">
+            <v>Oscar Piastri</v>
+          </cell>
+          <cell r="P24" t="str">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="J25" t="str">
+            <v>2</v>
+          </cell>
+          <cell r="L25" t="str">
+            <v>Max Verstappen</v>
+          </cell>
+          <cell r="P25" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26" t="str">
+            <v>3</v>
+          </cell>
+          <cell r="L26" t="str">
+            <v>Charles Leclerc</v>
+          </cell>
+          <cell r="P26" t="str">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="J27" t="str">
+            <v>4</v>
+          </cell>
+          <cell r="L27" t="str">
+            <v>Lando Norris</v>
+          </cell>
+          <cell r="P27" t="str">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="J28" t="str">
+            <v>5</v>
+          </cell>
+          <cell r="L28" t="str">
+            <v>George Russell</v>
+          </cell>
+          <cell r="P28" t="str">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="J29" t="str">
+            <v>6</v>
+          </cell>
+          <cell r="L29" t="str">
+            <v>Andrea Kimi Antonelli</v>
+          </cell>
+          <cell r="P29" t="str">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="J30" t="str">
+            <v>7</v>
+          </cell>
+          <cell r="L30" t="str">
+            <v>Lewis Hamilton</v>
+          </cell>
+          <cell r="P30" t="str">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31" t="str">
+            <v>8</v>
+          </cell>
+          <cell r="L31" t="str">
+            <v>Carlos Sainz Jr.</v>
+          </cell>
+          <cell r="P31" t="str">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="J32" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="L32" t="str">
+            <v>Alexander Albon</v>
+          </cell>
+          <cell r="P32" t="str">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="J33" t="str">
+            <v>10</v>
+          </cell>
+          <cell r="L33" t="str">
+            <v>Isack Hadjar</v>
+          </cell>
+          <cell r="P33" t="str">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="J34" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="L34" t="str">
+            <v>Fernando Alonso</v>
+          </cell>
+          <cell r="P34" t="str">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="J35" t="str">
+            <v>12</v>
+          </cell>
+          <cell r="L35" t="str">
+            <v>Liam Lawson</v>
+          </cell>
+          <cell r="P35" t="str">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="J36" t="str">
+            <v>13</v>
+          </cell>
+          <cell r="L36" t="str">
+            <v>Oliver Bearman</v>
+          </cell>
+          <cell r="P36" t="str">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="L37" t="str">
+            <v>Esteban Ocon</v>
+          </cell>
+          <cell r="P37" t="str">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="J38" t="str">
+            <v>15</v>
+          </cell>
+          <cell r="L38" t="str">
+            <v>Nico Hülkenberg</v>
+          </cell>
+          <cell r="P38" t="str">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="J39" t="str">
+            <v>16</v>
+          </cell>
+          <cell r="L39" t="str">
+            <v>Lance Stroll</v>
+          </cell>
+          <cell r="P39" t="str">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="J40" t="str">
+            <v>17</v>
+          </cell>
+          <cell r="L40" t="str">
+            <v>Jack Doohan</v>
+          </cell>
+          <cell r="P40" t="str">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="J41" t="str">
+            <v>18</v>
+          </cell>
+          <cell r="L41" t="str">
+            <v>Gabriel Bortoleto</v>
+          </cell>
+          <cell r="P41" t="str">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="J42" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L42" t="str">
+            <v>Yuki Tsunoda</v>
+          </cell>
+          <cell r="P42" t="str">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="J43" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L43" t="str">
+            <v>Pierre Gasly</v>
+          </cell>
+          <cell r="P43" t="str">
+            <v>9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6">
+        <row r="24">
+          <cell r="J24" t="str">
+            <v>1</v>
+          </cell>
+          <cell r="L24" t="str">
+            <v>Lando Norris</v>
+          </cell>
+          <cell r="P24">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="J25" t="str">
+            <v>2</v>
+          </cell>
+          <cell r="L25" t="str">
+            <v>Oscar Piastri</v>
+          </cell>
+          <cell r="P25" t="str">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26" t="str">
+            <v>3</v>
+          </cell>
+          <cell r="L26" t="str">
+            <v>Lewis Hamilton</v>
+          </cell>
+          <cell r="P26" t="str">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="J27" t="str">
+            <v>4</v>
+          </cell>
+          <cell r="L27" t="str">
+            <v>George Russell</v>
+          </cell>
+          <cell r="P27" t="str">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="J28" t="str">
+            <v>5</v>
+          </cell>
+          <cell r="L28" t="str">
+            <v>Lance Stroll</v>
+          </cell>
+          <cell r="P28" t="str">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="J29" t="str">
+            <v>6</v>
+          </cell>
+          <cell r="L29" t="str">
+            <v>Yuki Tsunoda</v>
+          </cell>
+          <cell r="P29" t="str">
+            <v>PL</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="J30" t="str">
+            <v>7</v>
+          </cell>
+          <cell r="L30" t="str">
+            <v>Andrea Kimi Antonelli</v>
+          </cell>
+          <cell r="P30" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31" t="str">
+            <v>8</v>
+          </cell>
+          <cell r="L31" t="str">
+            <v>Pierre Gasly</v>
+          </cell>
+          <cell r="P31" t="str">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="J32" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="L32" t="str">
+            <v>Nico Hülkenberg</v>
+          </cell>
+          <cell r="P32" t="str">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="J33" t="str">
+            <v>10</v>
+          </cell>
+          <cell r="L33" t="str">
+            <v>Isack Hadjar</v>
+          </cell>
+          <cell r="P33" t="str">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="J34" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="L34" t="str">
+            <v>Alexander Albon</v>
+          </cell>
+          <cell r="P34" t="str">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="J35" t="str">
+            <v>12</v>
+          </cell>
+          <cell r="L35" t="str">
+            <v>Esteban Ocon</v>
+          </cell>
+          <cell r="P35" t="str">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="J36" t="str">
+            <v>13</v>
+          </cell>
+          <cell r="L36" t="str">
+            <v>Liam Lawson</v>
+          </cell>
+          <cell r="P36" t="str">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="L37" t="str">
+            <v>Oliver Bearman</v>
+          </cell>
+          <cell r="P37" t="str">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="J38" t="str">
+            <v>15</v>
+          </cell>
+          <cell r="L38" t="str">
+            <v>Gabriel Bortoleto</v>
+          </cell>
+          <cell r="P38" t="str">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="J39" t="str">
+            <v>16</v>
+          </cell>
+          <cell r="L39" t="str">
+            <v>Jack Doohan</v>
+          </cell>
+          <cell r="P39" t="str">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="J40" t="str">
+            <v>17</v>
+          </cell>
+          <cell r="L40" t="str">
+            <v>Max Verstappen</v>
+          </cell>
+          <cell r="P40" t="str">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="J41" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L41" t="str">
+            <v>Fernando Alonso</v>
+          </cell>
+          <cell r="P41" t="str">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="J42" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L42" t="str">
+            <v>Carlos Sainz Jr.</v>
+          </cell>
+          <cell r="P42" t="str">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="J43" t="str">
+            <v>DNS5</v>
+          </cell>
+          <cell r="L43" t="str">
+            <v>Charles Leclerc</v>
+          </cell>
+          <cell r="P43" t="str">
+            <v>—5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
+        <row r="24">
+          <cell r="J24" t="str">
+            <v>1</v>
+          </cell>
+          <cell r="L24" t="str">
+            <v>Lando Norris</v>
+          </cell>
+          <cell r="P24">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="J25" t="str">
+            <v>2</v>
+          </cell>
+          <cell r="L25" t="str">
+            <v>Charles Leclerc</v>
+          </cell>
+          <cell r="P25">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26" t="str">
+            <v>3</v>
+          </cell>
+          <cell r="L26" t="str">
+            <v>Oscar Piastri</v>
+          </cell>
+          <cell r="P26">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="J27" t="str">
+            <v>4</v>
+          </cell>
+          <cell r="L27" t="str">
+            <v>Max Verstappen</v>
+          </cell>
+          <cell r="P27">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="J28" t="str">
+            <v>5</v>
+          </cell>
+          <cell r="L28" t="str">
+            <v>Lewis Hamilton</v>
+          </cell>
+          <cell r="P28">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="J29" t="str">
+            <v>6</v>
+          </cell>
+          <cell r="L29" t="str">
+            <v>Isack Hadjar</v>
+          </cell>
+          <cell r="P29">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="J30" t="str">
+            <v>7</v>
+          </cell>
+          <cell r="L30" t="str">
+            <v>Esteban Ocon</v>
+          </cell>
+          <cell r="P30">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31" t="str">
+            <v>8</v>
+          </cell>
+          <cell r="L31" t="str">
+            <v>Liam Lawson</v>
+          </cell>
+          <cell r="P31">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="J32" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="L32" t="str">
+            <v>Alexander Albon</v>
+          </cell>
+          <cell r="P32">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="J33" t="str">
+            <v>10</v>
+          </cell>
+          <cell r="L33" t="str">
+            <v>Carlos Sainz Jr.</v>
+          </cell>
+          <cell r="P33">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="J34" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="L34" t="str">
+            <v>George Russell</v>
+          </cell>
+          <cell r="P34">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="J35" t="str">
+            <v>12</v>
+          </cell>
+          <cell r="L35" t="str">
+            <v>Oliver Bearman</v>
+          </cell>
+          <cell r="P35">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="J36" t="str">
+            <v>13</v>
+          </cell>
+          <cell r="L36" t="str">
+            <v>Franco Colapinto</v>
+          </cell>
+          <cell r="P36">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="J37" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="L37" t="str">
+            <v>Gabriel Bortoleto</v>
+          </cell>
+          <cell r="P37">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="J38" t="str">
+            <v>15</v>
+          </cell>
+          <cell r="L38" t="str">
+            <v>Lance Stroll</v>
+          </cell>
+          <cell r="P38">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="J39" t="str">
+            <v>16</v>
+          </cell>
+          <cell r="L39" t="str">
+            <v>Nico Hülkenberg</v>
+          </cell>
+          <cell r="P39">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="J40" t="str">
+            <v>17</v>
+          </cell>
+          <cell r="L40" t="str">
+            <v>Yuki Tsunoda</v>
+          </cell>
+          <cell r="P40">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="J41" t="str">
+            <v>18</v>
+          </cell>
+          <cell r="L41" t="str">
+            <v>Andrea Kimi Antonelli</v>
+          </cell>
+          <cell r="P41">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="J42" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L42" t="str">
+            <v>Fernando Alonso</v>
+          </cell>
+          <cell r="P42">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="J43" t="str">
+            <v>Ret</v>
+          </cell>
+          <cell r="L43" t="str">
+            <v>Pierre Gasly</v>
+          </cell>
+          <cell r="P43">
+            <v>17</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2198,140 +4271,142 @@
     <tableColumn id="2" xr3:uid="{A2C1729C-5A9F-4F3B-9D25-29460232C8BB}" name="Circuit Name" dataDxfId="98"/>
     <tableColumn id="3" xr3:uid="{CDE8E4A3-91F0-42E8-9535-50FE31EF16BE}" name="Location" dataDxfId="97"/>
     <tableColumn id="4" xr3:uid="{15A0D957-CB98-4793-9130-02DA6096C7EE}" name="Race Date" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{5C322528-271F-4EDD-8D7B-6FAE995790B5}" name="Distance" dataDxfId="95"/>
-    <tableColumn id="6" xr3:uid="{E39D53C2-53BA-4179-9C6E-AD4D5427D7C5}" name="Fastest Time" dataDxfId="94"/>
-    <tableColumn id="7" xr3:uid="{61ABA8A6-ABC2-4008-93AA-C07FC2524B57}" name="1" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{91B3BA5A-8F2D-45BB-B42E-FCE1231D8296}" name="2" dataDxfId="92"/>
-    <tableColumn id="9" xr3:uid="{208C354C-D504-490A-9A6E-F1C70382A1BD}" name="3" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{5C322528-271F-4EDD-8D7B-6FAE995790B5}" name="Distance" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E39D53C2-53BA-4179-9C6E-AD4D5427D7C5}" name="Fastest Time" dataDxfId="0">
+      <calculatedColumnFormula>[1]Australian_Grand_Prix!$O$24</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{61ABA8A6-ABC2-4008-93AA-C07FC2524B57}" name="1" dataDxfId="95"/>
+    <tableColumn id="8" xr3:uid="{91B3BA5A-8F2D-45BB-B42E-FCE1231D8296}" name="2" dataDxfId="94"/>
+    <tableColumn id="9" xr3:uid="{208C354C-D504-490A-9A6E-F1C70382A1BD}" name="3" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}" name="Table4" displayName="Table4" ref="A1:Y44" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}" name="Table4" displayName="Table4" ref="A1:Y44" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
   <autoFilter ref="A1:Y44" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{CF33613A-B550-44CB-881B-6F14CACD5B72}" name="Driver" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{64862BF4-56F0-4709-A8AB-C085BAF0215A}" name="Australian Grand Prix" dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{2D3377A0-58D7-467A-99BD-8DD5E5195992}" name="Chinese Grand Prix" dataDxfId="86"/>
-    <tableColumn id="5" xr3:uid="{0ECE7874-3069-4E86-A858-526B2561A56E}" name="Japanese Grand Prix" dataDxfId="85"/>
-    <tableColumn id="6" xr3:uid="{3332362F-E796-4D76-B72D-D37A9E8C4506}" name="Bahrain Grand Prix" dataDxfId="84"/>
-    <tableColumn id="7" xr3:uid="{6A873417-5AFE-4D0F-88A9-6011AD971FED}" name="Saudi Arabian Grand Prix" dataDxfId="83"/>
-    <tableColumn id="8" xr3:uid="{2384B2F0-E1B8-4D15-A86A-C506AC2DDE75}" name="Miami Grand Prix" dataDxfId="82"/>
-    <tableColumn id="9" xr3:uid="{A4F6721E-F16D-4038-BD64-3E8A7D38B02F}" name="Emilia Romagna Grand Prix" dataDxfId="81"/>
-    <tableColumn id="10" xr3:uid="{435C1CC1-7C35-4D05-B75A-E2D3EA9487F5}" name="Monaco Grand Prix" dataDxfId="80"/>
-    <tableColumn id="11" xr3:uid="{7324DE86-EE77-4D97-944F-558B5246B501}" name="Spanish Grand Prix" dataDxfId="79"/>
-    <tableColumn id="12" xr3:uid="{B0654BA4-C5FE-40FC-94D4-F2829B439C83}" name="Canadian Grand Prix" dataDxfId="78"/>
-    <tableColumn id="13" xr3:uid="{40A2DB89-A1EF-4668-BB5F-0C8F41981CE9}" name="Austrian Grand Prix" dataDxfId="77"/>
-    <tableColumn id="14" xr3:uid="{7E4C0B80-60BB-443B-B58C-2C484E838E2D}" name="British Grand Prix" dataDxfId="76"/>
-    <tableColumn id="15" xr3:uid="{D7685E94-DED7-4922-8549-80717F6854B8}" name="Belgian Grand Prix" dataDxfId="75"/>
-    <tableColumn id="16" xr3:uid="{E8B67644-354D-4320-AEE9-C7236B9F7A62}" name="Hungarian Grand Prix" dataDxfId="74"/>
-    <tableColumn id="17" xr3:uid="{9744C7B8-818D-4DE8-B37D-EFBCC20F2D87}" name="Dutch Grand Prix" dataDxfId="73"/>
-    <tableColumn id="18" xr3:uid="{EF67C45C-CAC1-4298-A58A-EEA09E9B8331}" name="Italian Grand Prix" dataDxfId="72"/>
-    <tableColumn id="19" xr3:uid="{298F9D14-379A-45B8-8779-FD50639B978E}" name="Azerbaijan Grand Prix" dataDxfId="71"/>
-    <tableColumn id="20" xr3:uid="{A88F8700-7FAE-4431-8633-EE182CD448DA}" name="Singapore Grand Prix" dataDxfId="70"/>
-    <tableColumn id="21" xr3:uid="{EDA628AE-0844-4D1C-9A31-622106A74B74}" name="United States Grand Prix" dataDxfId="69"/>
-    <tableColumn id="22" xr3:uid="{40DA2915-5603-475B-B8B3-83784AE5046E}" name="Mexico City Grand Prix" dataDxfId="68"/>
-    <tableColumn id="23" xr3:uid="{46622AFA-DB78-4AE5-89D9-F1D3556D5A3D}" name="São Paulo Grand Prix" dataDxfId="67"/>
-    <tableColumn id="24" xr3:uid="{3EC53053-E45B-44EE-AC6B-F7BB5EB7B9F5}" name="Las Vegas Grand Prix" dataDxfId="66"/>
-    <tableColumn id="25" xr3:uid="{6F3819A8-BF88-4B0C-9F74-4EE092BA245E}" name="Qatar Grand Prix" dataDxfId="65"/>
-    <tableColumn id="26" xr3:uid="{6A29A013-FF84-400E-8F74-E5A850484E6D}" name="Abu Dhabi Grand Prix" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{CF33613A-B550-44CB-881B-6F14CACD5B72}" name="Driver" dataDxfId="90"/>
+    <tableColumn id="3" xr3:uid="{64862BF4-56F0-4709-A8AB-C085BAF0215A}" name="Australian Grand Prix" dataDxfId="89"/>
+    <tableColumn id="4" xr3:uid="{2D3377A0-58D7-467A-99BD-8DD5E5195992}" name="Chinese Grand Prix" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{0ECE7874-3069-4E86-A858-526B2561A56E}" name="Japanese Grand Prix" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{3332362F-E796-4D76-B72D-D37A9E8C4506}" name="Bahrain Grand Prix" dataDxfId="86"/>
+    <tableColumn id="7" xr3:uid="{6A873417-5AFE-4D0F-88A9-6011AD971FED}" name="Saudi Arabian Grand Prix" dataDxfId="85"/>
+    <tableColumn id="8" xr3:uid="{2384B2F0-E1B8-4D15-A86A-C506AC2DDE75}" name="Miami Grand Prix" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{A4F6721E-F16D-4038-BD64-3E8A7D38B02F}" name="Emilia Romagna Grand Prix" dataDxfId="83"/>
+    <tableColumn id="10" xr3:uid="{435C1CC1-7C35-4D05-B75A-E2D3EA9487F5}" name="Monaco Grand Prix" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{7324DE86-EE77-4D97-944F-558B5246B501}" name="Spanish Grand Prix" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{B0654BA4-C5FE-40FC-94D4-F2829B439C83}" name="Canadian Grand Prix" dataDxfId="80"/>
+    <tableColumn id="13" xr3:uid="{40A2DB89-A1EF-4668-BB5F-0C8F41981CE9}" name="Austrian Grand Prix" dataDxfId="79"/>
+    <tableColumn id="14" xr3:uid="{7E4C0B80-60BB-443B-B58C-2C484E838E2D}" name="British Grand Prix" dataDxfId="78"/>
+    <tableColumn id="15" xr3:uid="{D7685E94-DED7-4922-8549-80717F6854B8}" name="Belgian Grand Prix" dataDxfId="77"/>
+    <tableColumn id="16" xr3:uid="{E8B67644-354D-4320-AEE9-C7236B9F7A62}" name="Hungarian Grand Prix" dataDxfId="76"/>
+    <tableColumn id="17" xr3:uid="{9744C7B8-818D-4DE8-B37D-EFBCC20F2D87}" name="Dutch Grand Prix" dataDxfId="75"/>
+    <tableColumn id="18" xr3:uid="{EF67C45C-CAC1-4298-A58A-EEA09E9B8331}" name="Italian Grand Prix" dataDxfId="74"/>
+    <tableColumn id="19" xr3:uid="{298F9D14-379A-45B8-8779-FD50639B978E}" name="Azerbaijan Grand Prix" dataDxfId="73"/>
+    <tableColumn id="20" xr3:uid="{A88F8700-7FAE-4431-8633-EE182CD448DA}" name="Singapore Grand Prix" dataDxfId="72"/>
+    <tableColumn id="21" xr3:uid="{EDA628AE-0844-4D1C-9A31-622106A74B74}" name="United States Grand Prix" dataDxfId="71"/>
+    <tableColumn id="22" xr3:uid="{40DA2915-5603-475B-B8B3-83784AE5046E}" name="Mexico City Grand Prix" dataDxfId="70"/>
+    <tableColumn id="23" xr3:uid="{46622AFA-DB78-4AE5-89D9-F1D3556D5A3D}" name="São Paulo Grand Prix" dataDxfId="69"/>
+    <tableColumn id="24" xr3:uid="{3EC53053-E45B-44EE-AC6B-F7BB5EB7B9F5}" name="Las Vegas Grand Prix" dataDxfId="68"/>
+    <tableColumn id="25" xr3:uid="{6F3819A8-BF88-4B0C-9F74-4EE092BA245E}" name="Qatar Grand Prix" dataDxfId="67"/>
+    <tableColumn id="26" xr3:uid="{6A29A013-FF84-400E-8F74-E5A850484E6D}" name="Abu Dhabi Grand Prix" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}" name="Table5" displayName="Table5" ref="A1:E21" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
-  <autoFilter ref="A1:E21" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D9288ECF-7FB6-413D-B1F9-D0C1F542379A}" name="Team Name" dataDxfId="61">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$21,Drivers!$C$2:$C$21,"")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}" name="Table6" displayName="Table6" ref="A1:AA44" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+  <autoFilter ref="A1:AA44" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}"/>
+  <tableColumns count="27">
+    <tableColumn id="1" xr3:uid="{E278D08B-82F0-48D0-A658-DE818A33E0B8}" name="Driver" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{00D7725B-DFFE-4C3A-ACCE-32C162A4E831}" name="Constructor" dataDxfId="55">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9F22078D-54A1-4A4A-AF23-B4137F60AB3E}" name="Constructor" dataDxfId="60">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$21,Drivers!$F$2:$F$21,"")</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{8FDBF4AD-2961-4047-8F65-8E8ADEDC3502}" name="Team" dataDxfId="54">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8E3FB958-7BB0-400F-A3F5-E8EC1EDBE678}" name="Driver" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{386A61E9-CDA2-4647-81AE-9E7EE26F203F}" name="Engine/Power Unit" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{FECB8E79-446F-4614-9058-29E64F3CE65C}" name="Chassis" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{FEF76843-A12B-4494-995B-783FB04E6013}" name="Australian Grand Prix" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{17071EA5-F41C-4EBD-94F0-1B51429AF44F}" name="Chinese Grand Prix" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{F5001349-A1D5-43C9-97E1-9460CA742B63}" name="Japanese Grand Prix" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{6D0913D3-24E1-4ACA-B912-74174373B813}" name="Bahrain Grand Prix" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{E4C84672-BC98-4DF5-B9EE-8A8055F39F2D}" name="Saudi Arabian Grand Prix" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{BB7D339C-688A-4E60-8767-047C06319E68}" name="Miami Grand Prix" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{57075CE6-6548-4845-A50E-8AEFC61753A4}" name="Emilia Romagna Grand Prix" dataDxfId="47"/>
+    <tableColumn id="11" xr3:uid="{EE6736F8-ADB5-4E71-B05F-97594B3B3472}" name="Monaco Grand Prix" dataDxfId="46"/>
+    <tableColumn id="12" xr3:uid="{7968AD0F-F03C-43FE-9936-B9C133C05B68}" name="Spanish Grand Prix" dataDxfId="45"/>
+    <tableColumn id="13" xr3:uid="{B8990854-8E63-4954-BB66-C62E6A969529}" name="Canadian Grand Prix" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{0E25BBA9-F83B-4D7F-B1E2-448AE6406574}" name="Austrian Grand Prix" dataDxfId="43"/>
+    <tableColumn id="15" xr3:uid="{AFBF197F-D2AA-4D23-9095-09D50B18B3F7}" name="British Grand Prix" dataDxfId="42"/>
+    <tableColumn id="16" xr3:uid="{CF02CCED-BF33-4C52-A70B-20F8601C2B11}" name="Belgian Grand Prix" dataDxfId="41"/>
+    <tableColumn id="17" xr3:uid="{7104019E-E290-4E2A-85C1-75D032C22FCE}" name="Hungarian Grand Prix" dataDxfId="40"/>
+    <tableColumn id="18" xr3:uid="{FFF263A4-5EE2-49F0-9BA6-08425F3D3FE9}" name="Dutch Grand Prix" dataDxfId="39"/>
+    <tableColumn id="19" xr3:uid="{0A2EFD7F-EE8D-449A-ADD0-4CCC316EBCE8}" name="Italian Grand Prix" dataDxfId="38"/>
+    <tableColumn id="20" xr3:uid="{EB37AA19-112E-41AF-8572-4A071B7C2217}" name="Azerbaijan Grand Prix" dataDxfId="37"/>
+    <tableColumn id="21" xr3:uid="{E5F20E2D-66D0-473E-B944-BB69CCC67E52}" name="Singapore Grand Prix" dataDxfId="36"/>
+    <tableColumn id="22" xr3:uid="{2C2EEBC6-3F36-4C36-B283-0B40A3DEF047}" name="United States Grand Prix" dataDxfId="35"/>
+    <tableColumn id="23" xr3:uid="{F863F260-3241-4267-96F8-B19D16BA264E}" name="Mexico City Grand Prix" dataDxfId="34"/>
+    <tableColumn id="24" xr3:uid="{9076A145-7D0A-4875-BB6A-4FB7D295FC47}" name="São Paulo Grand Prix" dataDxfId="33"/>
+    <tableColumn id="25" xr3:uid="{E68C8DA5-1B26-4FD9-A9B3-04738D5CD8FB}" name="Las Vegas Grand Prix" dataDxfId="32"/>
+    <tableColumn id="26" xr3:uid="{149AD907-AF11-4CF7-A5B7-75B2C9170D15}" name="Qatar Grand Prix" dataDxfId="31"/>
+    <tableColumn id="27" xr3:uid="{940BCA92-8A19-4BC4-979F-FC730E0FF0D9}" name="Abu Dhabi Grand Prix" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}" name="Table6" displayName="Table6" ref="A1:AA44" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A1:AA44" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}"/>
-  <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{E278D08B-82F0-48D0-A658-DE818A33E0B8}" name="Driver" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{00D7725B-DFFE-4C3A-ACCE-32C162A4E831}" name="Constructor" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}" name="Table7" displayName="Table7" ref="A1:Z21" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:Z21" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}"/>
+  <tableColumns count="26">
+    <tableColumn id="1" xr3:uid="{04FE50CB-43CC-4C2C-B3E5-20381A77C6EE}" name="Driver" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{6F987E8C-773F-4CD7-8683-D3D2A2357DFC}" name="Constructor" dataDxfId="26">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8FDBF4AD-2961-4047-8F65-8E8ADEDC3502}" name="Team" dataDxfId="52">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{FEF76843-A12B-4494-995B-783FB04E6013}" name="Australian Grand Prix" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{17071EA5-F41C-4EBD-94F0-1B51429AF44F}" name="Chinese Grand Prix" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{F5001349-A1D5-43C9-97E1-9460CA742B63}" name="Japanese Grand Prix" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{6D0913D3-24E1-4ACA-B912-74174373B813}" name="Bahrain Grand Prix" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{E4C84672-BC98-4DF5-B9EE-8A8055F39F2D}" name="Saudi Arabian Grand Prix" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{BB7D339C-688A-4E60-8767-047C06319E68}" name="Miami Grand Prix" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{57075CE6-6548-4845-A50E-8AEFC61753A4}" name="Emilia Romagna Grand Prix" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{EE6736F8-ADB5-4E71-B05F-97594B3B3472}" name="Monaco Grand Prix" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{7968AD0F-F03C-43FE-9936-B9C133C05B68}" name="Spanish Grand Prix" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{B8990854-8E63-4954-BB66-C62E6A969529}" name="Canadian Grand Prix" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{0E25BBA9-F83B-4D7F-B1E2-448AE6406574}" name="Austrian Grand Prix" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{AFBF197F-D2AA-4D23-9095-09D50B18B3F7}" name="British Grand Prix" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{CF02CCED-BF33-4C52-A70B-20F8601C2B11}" name="Belgian Grand Prix" dataDxfId="39"/>
-    <tableColumn id="17" xr3:uid="{7104019E-E290-4E2A-85C1-75D032C22FCE}" name="Hungarian Grand Prix" dataDxfId="38"/>
-    <tableColumn id="18" xr3:uid="{FFF263A4-5EE2-49F0-9BA6-08425F3D3FE9}" name="Dutch Grand Prix" dataDxfId="37"/>
-    <tableColumn id="19" xr3:uid="{0A2EFD7F-EE8D-449A-ADD0-4CCC316EBCE8}" name="Italian Grand Prix" dataDxfId="36"/>
-    <tableColumn id="20" xr3:uid="{EB37AA19-112E-41AF-8572-4A071B7C2217}" name="Azerbaijan Grand Prix" dataDxfId="35"/>
-    <tableColumn id="21" xr3:uid="{E5F20E2D-66D0-473E-B944-BB69CCC67E52}" name="Singapore Grand Prix" dataDxfId="34"/>
-    <tableColumn id="22" xr3:uid="{2C2EEBC6-3F36-4C36-B283-0B40A3DEF047}" name="United States Grand Prix" dataDxfId="33"/>
-    <tableColumn id="23" xr3:uid="{F863F260-3241-4267-96F8-B19D16BA264E}" name="Mexico City Grand Prix" dataDxfId="32"/>
-    <tableColumn id="24" xr3:uid="{9076A145-7D0A-4875-BB6A-4FB7D295FC47}" name="São Paulo Grand Prix" dataDxfId="31"/>
-    <tableColumn id="25" xr3:uid="{E68C8DA5-1B26-4FD9-A9B3-04738D5CD8FB}" name="Las Vegas Grand Prix" dataDxfId="30"/>
-    <tableColumn id="26" xr3:uid="{149AD907-AF11-4CF7-A5B7-75B2C9170D15}" name="Qatar Grand Prix" dataDxfId="29"/>
-    <tableColumn id="27" xr3:uid="{940BCA92-8A19-4BC4-979F-FC730E0FF0D9}" name="Abu Dhabi Grand Prix" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{F55A6B37-6EDE-41E4-B6B2-EE2FF245418C}" name="Australian Grand Prix" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{07D64B60-38BF-49D0-9F5A-DA0EB0A1CF21}" name="Chinese Grand Prix" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{1D828739-4FD5-40ED-A5B5-B23567BDE3FE}" name="Japanese Grand Prix" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{1062B4A0-6DF4-41F9-877D-4B43E48CCFE6}" name="Bahrain Grand Prix" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{1C734CE0-74E1-4F37-8C9E-9F2EE741BFE5}" name="Saudi Arabian Grand Prix" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{6DA07DD4-DD0E-4DB7-AEA7-F3A2E9225738}" name="Miami Grand Prix" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{257ED334-DEA1-4225-A408-3C2676795930}" name="Emilia Romagna Grand Prix" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{BAE89735-07AF-444C-B220-851C0CB3C754}" name="Monaco Grand Prix" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{B7D94A29-43B7-41DC-80C3-B1923F3E9284}" name="Spanish Grand Prix" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{21AA035A-318D-4FB7-BBBA-0C6D4F13E5CB}" name="Canadian Grand Prix" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{FACD5626-3EE1-4F7A-B7CB-6C80DE689297}" name="Austrian Grand Prix" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{D0953B36-F941-4B38-8251-D2477280E99D}" name="British Grand Prix" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{AC25F154-2768-4FDF-8473-44B8EF96F3F9}" name="Belgian Grand Prix" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{06BB5252-52C6-48F1-92DD-3677D94F6AD6}" name="Hungarian Grand Prix" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{6FCED645-DEDA-4065-8ED7-3401FF6E8A64}" name="Dutch Grand Prix" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{66976D97-649B-4E27-84FB-6BBBDE6B54DD}" name="Italian Grand Prix" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{41283C26-AE5C-4033-8465-C5C3B22E6094}" name="Azerbaijan Grand Prix" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{C4FE0C5A-0BCF-477D-ABC0-0A0D0583E97C}" name="Singapore Grand Prix" dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{F69B7691-4E40-4AE7-846B-7BA48ADEE249}" name="United States Grand Prix" dataDxfId="7"/>
+    <tableColumn id="22" xr3:uid="{B7417A28-B404-40D9-AFF3-00A8B4A0C4D2}" name="Mexico City Grand Prix" dataDxfId="6"/>
+    <tableColumn id="23" xr3:uid="{FE4AA98D-B3DC-4364-BC04-FAE369D83855}" name="São Paulo Grand Prix" dataDxfId="5"/>
+    <tableColumn id="24" xr3:uid="{BCBF9F5E-E462-49BA-87E9-6620D01608A4}" name="Las Vegas Grand Prix" dataDxfId="4"/>
+    <tableColumn id="25" xr3:uid="{5963F622-6118-42F5-BD17-0A2B097489EC}" name="Qatar Grand Prix" dataDxfId="3"/>
+    <tableColumn id="26" xr3:uid="{2B6C136A-A691-419C-9E4E-23006C9A0B32}" name="Abu Dhabi Grand Prix" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}" name="Table7" displayName="Table7" ref="A1:Z21" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A1:Z21" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}"/>
-  <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{04FE50CB-43CC-4C2C-B3E5-20381A77C6EE}" name="Driver" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{6F987E8C-773F-4CD7-8683-D3D2A2357DFC}" name="Constructor" dataDxfId="24">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}" name="Table5" displayName="Table5" ref="A1:E21" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+  <autoFilter ref="A1:E21" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D9288ECF-7FB6-413D-B1F9-D0C1F542379A}" name="Team Name" dataDxfId="63">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$21,Drivers!$C$2:$C$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F55A6B37-6EDE-41E4-B6B2-EE2FF245418C}" name="Australian Grand Prix" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{07D64B60-38BF-49D0-9F5A-DA0EB0A1CF21}" name="Chinese Grand Prix" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{1D828739-4FD5-40ED-A5B5-B23567BDE3FE}" name="Japanese Grand Prix" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{1062B4A0-6DF4-41F9-877D-4B43E48CCFE6}" name="Bahrain Grand Prix" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{1C734CE0-74E1-4F37-8C9E-9F2EE741BFE5}" name="Saudi Arabian Grand Prix" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{6DA07DD4-DD0E-4DB7-AEA7-F3A2E9225738}" name="Miami Grand Prix" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{257ED334-DEA1-4225-A408-3C2676795930}" name="Emilia Romagna Grand Prix" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{BAE89735-07AF-444C-B220-851C0CB3C754}" name="Monaco Grand Prix" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{B7D94A29-43B7-41DC-80C3-B1923F3E9284}" name="Spanish Grand Prix" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{21AA035A-318D-4FB7-BBBA-0C6D4F13E5CB}" name="Canadian Grand Prix" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{FACD5626-3EE1-4F7A-B7CB-6C80DE689297}" name="Austrian Grand Prix" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{D0953B36-F941-4B38-8251-D2477280E99D}" name="British Grand Prix" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{AC25F154-2768-4FDF-8473-44B8EF96F3F9}" name="Belgian Grand Prix" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{06BB5252-52C6-48F1-92DD-3677D94F6AD6}" name="Hungarian Grand Prix" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{6FCED645-DEDA-4065-8ED7-3401FF6E8A64}" name="Dutch Grand Prix" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{66976D97-649B-4E27-84FB-6BBBDE6B54DD}" name="Italian Grand Prix" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{41283C26-AE5C-4033-8465-C5C3B22E6094}" name="Azerbaijan Grand Prix" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{C4FE0C5A-0BCF-477D-ABC0-0A0D0583E97C}" name="Singapore Grand Prix" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{F69B7691-4E40-4AE7-846B-7BA48ADEE249}" name="United States Grand Prix" dataDxfId="5"/>
-    <tableColumn id="22" xr3:uid="{B7417A28-B404-40D9-AFF3-00A8B4A0C4D2}" name="Mexico City Grand Prix" dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{FE4AA98D-B3DC-4364-BC04-FAE369D83855}" name="São Paulo Grand Prix" dataDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{BCBF9F5E-E462-49BA-87E9-6620D01608A4}" name="Las Vegas Grand Prix" dataDxfId="2"/>
-    <tableColumn id="25" xr3:uid="{5963F622-6118-42F5-BD17-0A2B097489EC}" name="Qatar Grand Prix" dataDxfId="1"/>
-    <tableColumn id="26" xr3:uid="{2B6C136A-A691-419C-9E4E-23006C9A0B32}" name="Abu Dhabi Grand Prix" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{9F22078D-54A1-4A4A-AF23-B4137F60AB3E}" name="Constructor" dataDxfId="62">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$21,Drivers!$F$2:$F$21,"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{8E3FB958-7BB0-400F-A3F5-E8EC1EDBE678}" name="Driver" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{386A61E9-CDA2-4647-81AE-9E7EE26F203F}" name="Engine/Power Unit" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{FECB8E79-446F-4614-9058-29E64F3CE65C}" name="Chassis" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2958,7 +5033,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836EF9E2-BFB4-48A6-9313-90407B9BAB5B}">
-  <dimension ref="B2:J26"/>
+  <dimension ref="B2:J57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="3" customWidth="1"/>
@@ -3014,6 +5089,9 @@
       <c r="E3" s="3" t="s">
         <v>114</v>
       </c>
+      <c r="F3" s="22">
+        <v>5.2779999999999996</v>
+      </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -3028,6 +5106,9 @@
       <c r="E4" s="3" t="s">
         <v>115</v>
       </c>
+      <c r="F4" s="22">
+        <v>5.4509999999999996</v>
+      </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
@@ -3042,6 +5123,9 @@
       <c r="E5" s="3" t="s">
         <v>116</v>
       </c>
+      <c r="F5" s="22">
+        <v>5.8070000000000004</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
@@ -3056,6 +5140,9 @@
       <c r="E6" s="3" t="s">
         <v>117</v>
       </c>
+      <c r="F6" s="22">
+        <v>5.4119999999999999</v>
+      </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
@@ -3070,6 +5157,9 @@
       <c r="E7" s="3" t="s">
         <v>118</v>
       </c>
+      <c r="F7" s="22">
+        <v>6.1740000000000004</v>
+      </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
@@ -3084,6 +5174,9 @@
       <c r="E8" s="3" t="s">
         <v>119</v>
       </c>
+      <c r="F8" s="22">
+        <v>5.4119999999999999</v>
+      </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
@@ -3098,6 +5191,9 @@
       <c r="E9" s="3" t="s">
         <v>120</v>
       </c>
+      <c r="F9" s="22">
+        <v>4.9089999999999998</v>
+      </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
@@ -3112,6 +5208,9 @@
       <c r="E10" s="3" t="s">
         <v>121</v>
       </c>
+      <c r="F10" s="22">
+        <v>3.3370000000000002</v>
+      </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
@@ -3126,6 +5225,9 @@
       <c r="E11" s="3" t="s">
         <v>122</v>
       </c>
+      <c r="F11" s="22">
+        <v>4.6749999999999998</v>
+      </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
@@ -3140,6 +5242,9 @@
       <c r="E12" s="3" t="s">
         <v>123</v>
       </c>
+      <c r="F12" s="22">
+        <v>4.3609999999999998</v>
+      </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
@@ -3154,6 +5259,9 @@
       <c r="E13" s="3" t="s">
         <v>124</v>
       </c>
+      <c r="F13" s="22">
+        <v>4.3179999999999996</v>
+      </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
@@ -3168,6 +5276,9 @@
       <c r="E14" s="3" t="s">
         <v>125</v>
       </c>
+      <c r="F14" s="22">
+        <v>5.891</v>
+      </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
@@ -3182,6 +5293,9 @@
       <c r="E15" s="3" t="s">
         <v>126</v>
       </c>
+      <c r="F15" s="22">
+        <v>7.0039999999999996</v>
+      </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
@@ -3196,8 +5310,11 @@
       <c r="E16" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="22">
+        <v>4.3810000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>153</v>
       </c>
@@ -3210,8 +5327,11 @@
       <c r="E17" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="22">
+        <v>4.2590000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>154</v>
       </c>
@@ -3224,8 +5344,11 @@
       <c r="E18" s="3" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="22">
+        <v>5.7930000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>155</v>
       </c>
@@ -3238,8 +5361,11 @@
       <c r="E19" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="22">
+        <v>6.0030000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>156</v>
       </c>
@@ -3252,8 +5378,11 @@
       <c r="E20" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="22">
+        <v>4.9279999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>157</v>
       </c>
@@ -3266,8 +5395,11 @@
       <c r="E21" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="22">
+        <v>5.5129999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>158</v>
       </c>
@@ -3280,8 +5412,11 @@
       <c r="E22" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="22">
+        <v>4.3040000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>159</v>
       </c>
@@ -3294,8 +5429,11 @@
       <c r="E23" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="22">
+        <v>4.3090000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>160</v>
       </c>
@@ -3308,8 +5446,11 @@
       <c r="E24" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="22">
+        <v>6.2009999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>161</v>
       </c>
@@ -3322,8 +5463,11 @@
       <c r="E25" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="22">
+        <v>5.4189999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>162</v>
       </c>
@@ -3336,11 +5480,221 @@
       <c r="E26" s="3" t="s">
         <v>137</v>
       </c>
+      <c r="F26" s="22">
+        <v>5.2809999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="I32" s="21"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="I33" s="21"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="I34" s="21"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="I35" s="21"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="I36" s="21"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="I37" s="21"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="I38" s="21"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="I39" s="21"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="I40" s="21"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="I41" s="21"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="I42" s="21"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="I43" s="21"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="I44" s="21"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="I45" s="21"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="I46" s="21"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="I47" s="21"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="I48" s="21"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="I49" s="21"/>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="I50" s="21"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="I51" s="21"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="I52" s="21"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="I53" s="21"/>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="I54" s="21"/>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="I55" s="21"/>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -3368,7 +5722,7 @@
     <col min="28" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" ht="130.19999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="6" customFormat="1" ht="129" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -3525,101 +5879,741 @@
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="B3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="C3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="E3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="F3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I3" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="B4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="E4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="F4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="G4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="H4" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="I4" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="B5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="C5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="D5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="E5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="F5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="I5" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="B6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="C6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="D6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>20</v>
+      </c>
+      <c r="E6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="F6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="G6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="H6" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I6" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="B7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="C7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="E7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="G7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>—5</v>
+      </c>
+      <c r="H7" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>—5</v>
+      </c>
+      <c r="I7" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="B8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="C8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="E8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="H8" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="I8" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="B9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="C9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="D9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="E9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="G9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="H9" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="I9" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="B10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>PL</v>
+      </c>
+      <c r="C10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="D10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="E10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>20</v>
+      </c>
+      <c r="F10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="G10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="H10" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="I10" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="B11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="C11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="D11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="F11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>20</v>
+      </c>
+      <c r="G11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="H11" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="I11" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="B12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="C12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>PL</v>
+      </c>
+      <c r="D12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="H12" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="I12" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="B13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="D13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="F13" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="G13" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="H13" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I13" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="B14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="E14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I14" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="B15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="C15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="D15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="E15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="F15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="B16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="C16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="D16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="E16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="F16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="H16" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I16" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="B17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>—1</v>
+      </c>
+      <c r="C17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="D17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="E17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="F17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="G17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="H17" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="I17" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="B18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="C18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="D18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="E18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="F18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="G18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>PL</v>
+      </c>
+      <c r="H18" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>PL</v>
+      </c>
+      <c r="I18" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="B19" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="C19" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D19" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="F19" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G19" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="H19" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="I19" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="B20" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>PL</v>
+      </c>
+      <c r="C20" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="D20" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="E20" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F20" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="G20" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="H20" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="I20" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="B21" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="C21" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="D21" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="E21" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="F21" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="G21" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="H21" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I21" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="B22" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="C22" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="D22" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="E22" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="F22" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="G22" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="H22" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="I22" s="9">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B24" s="10" t="s">
@@ -3699,100 +6693,740 @@
       <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="B25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="C25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>20</v>
+      </c>
+      <c r="D25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="E25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="F25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="G25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="H25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I25" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="B26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="C26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="D26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="E26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="F26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="G26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="H26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I26" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="B27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="C27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="D27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="E27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="F27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="G27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="H27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="I27" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="B28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="C28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="D28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>20</v>
+      </c>
+      <c r="E28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="F28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="G28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="H28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I28" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="B29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="C29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="D29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="E29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="F29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="G29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>DNS5</v>
+      </c>
+      <c r="H29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>DNS5</v>
+      </c>
+      <c r="I29" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="B30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="C30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="D30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="E30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="F30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="G30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="H30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I30" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="B31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="C31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="D31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="E31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="F31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="G31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="H31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="I31" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="C32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="D32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="E32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="F32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="G32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="H32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="I32" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="C33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="D33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="F33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>18</v>
+      </c>
+      <c r="G33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="H33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="C34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>19</v>
+      </c>
+      <c r="D34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="E34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>DSQ</v>
+      </c>
+      <c r="F34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>15</v>
+      </c>
+      <c r="G34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="H34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="I34" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="D35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="E35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="F35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="G35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="H35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I35" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="C36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="D36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="E36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="G36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="H36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I36" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="C37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="D37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="E37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="F37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="G37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="H37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>7</v>
+      </c>
+      <c r="I37" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="C38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="D38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="E38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="F38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="H38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+      <c r="I38" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>DNS1</v>
+      </c>
+      <c r="C39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="E39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="G39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="H39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
+      </c>
+      <c r="I39" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="C40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="D40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="E40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="F40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="G40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="H40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="I40" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="C41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>3</v>
+      </c>
+      <c r="D41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>1</v>
+      </c>
+      <c r="E41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>6</v>
+      </c>
+      <c r="F41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>2</v>
+      </c>
+      <c r="G41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="H41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="I41" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="C42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="D42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="E42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>16</v>
+      </c>
+      <c r="F42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="G42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="H42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>5</v>
+      </c>
+      <c r="C43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="D43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="E43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>12</v>
+      </c>
+      <c r="F43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+      <c r="G43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="H43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>11</v>
+      </c>
+      <c r="I43" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>38</v>
+      </c>
+      <c r="B44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="C44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>17</v>
+      </c>
+      <c r="D44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>14</v>
+      </c>
+      <c r="E44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="F44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>8</v>
+      </c>
+      <c r="G44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="H44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>Ret</v>
+      </c>
+      <c r="I44" s="9" t="str">
+        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3804,6 +7438,1541 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055D11F0-CC47-46EC-A6D6-C461ECA1696D}">
+  <dimension ref="A1:AA44"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" s="13" customFormat="1" ht="129.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" s="13" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA2" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Alpine-Renault</v>
+      </c>
+      <c r="C3" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>BWT Alpine Formula One Team</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Alpine-Renault</v>
+      </c>
+      <c r="C4" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>BWT Alpine Formula One Team</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Aston Martin Aramco-Mercedes</v>
+      </c>
+      <c r="C5" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Aston Martin Aramco Formula One Team</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Aston Martin Aramco-Mercedes</v>
+      </c>
+      <c r="C6" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Aston Martin Aramco Formula One Team</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Ferrari</v>
+      </c>
+      <c r="C7" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Scuderia Ferrari HP</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Ferrari</v>
+      </c>
+      <c r="C8" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Scuderia Ferrari HP</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Haas-Ferrari</v>
+      </c>
+      <c r="C9" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>MoneyGram Haas F1 Team</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Haas-Ferrari</v>
+      </c>
+      <c r="C10" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>MoneyGram Haas F1 Team</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Kick Sauber-Ferrari</v>
+      </c>
+      <c r="C11" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Stake F1 Team Kick Sauber</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Kick Sauber-Ferrari</v>
+      </c>
+      <c r="C12" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Stake F1 Team Kick Sauber</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>McLaren-Mercedes</v>
+      </c>
+      <c r="C13" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>McLaren Formula 1 Team</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>McLaren-Mercedes</v>
+      </c>
+      <c r="C14" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>McLaren Formula 1 Team</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Mercedes</v>
+      </c>
+      <c r="C15" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Mercedes-AMG Petronas Formula One Team</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Mercedes</v>
+      </c>
+      <c r="C16" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Mercedes-AMG Petronas Formula One Team</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Racing Bulls-Honda RBPT</v>
+      </c>
+      <c r="C17" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Visa Cash App Racing Bulls Formula One Team</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Racing Bulls-Honda RBPT</v>
+      </c>
+      <c r="C18" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Visa Cash App Racing Bulls Formula One Team</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Red Bull Racing-Honda RBPT</v>
+      </c>
+      <c r="C19" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Oracle Red Bull Racing</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Red Bull Racing-Honda RBPT</v>
+      </c>
+      <c r="C20" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Oracle Red Bull Racing</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Williams-Mercedes</v>
+      </c>
+      <c r="C21" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Williams Racing</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="J21" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Williams-Mercedes</v>
+      </c>
+      <c r="C22" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Williams Racing</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="P24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="S24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="T24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="V24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="W24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="X24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA24" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A25,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Alpine-Renault</v>
+      </c>
+      <c r="C25" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A25,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>BWT Alpine Formula One Team</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A26,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Alpine-Renault</v>
+      </c>
+      <c r="C26" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A26,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>BWT Alpine Formula One Team</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A27,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Aston Martin Aramco-Mercedes</v>
+      </c>
+      <c r="C27" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A27,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Aston Martin Aramco Formula One Team</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A28,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Aston Martin Aramco-Mercedes</v>
+      </c>
+      <c r="C28" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A28,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Aston Martin Aramco Formula One Team</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A29,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Ferrari</v>
+      </c>
+      <c r="C29" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A29,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Scuderia Ferrari HP</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A30,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Ferrari</v>
+      </c>
+      <c r="C30" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A30,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Scuderia Ferrari HP</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A31,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Haas-Ferrari</v>
+      </c>
+      <c r="C31" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A31,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>MoneyGram Haas F1 Team</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A32,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Haas-Ferrari</v>
+      </c>
+      <c r="C32" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A32,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>MoneyGram Haas F1 Team</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A33,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Kick Sauber-Ferrari</v>
+      </c>
+      <c r="C33" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A33,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Stake F1 Team Kick Sauber</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A34,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Kick Sauber-Ferrari</v>
+      </c>
+      <c r="C34" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A34,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Stake F1 Team Kick Sauber</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A35,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>McLaren-Mercedes</v>
+      </c>
+      <c r="C35" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A35,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>McLaren Formula 1 Team</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A36,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>McLaren-Mercedes</v>
+      </c>
+      <c r="C36" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A36,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>McLaren Formula 1 Team</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A37,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Mercedes</v>
+      </c>
+      <c r="C37" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A37,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Mercedes-AMG Petronas Formula One Team</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A38,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Mercedes</v>
+      </c>
+      <c r="C38" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A38,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Mercedes-AMG Petronas Formula One Team</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A39,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Racing Bulls-Honda RBPT</v>
+      </c>
+      <c r="C39" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A39,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Visa Cash App Racing Bulls Formula One Team</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A40,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Racing Bulls-Honda RBPT</v>
+      </c>
+      <c r="C40" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A40,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Visa Cash App Racing Bulls Formula One Team</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A41,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Red Bull Racing-Honda RBPT</v>
+      </c>
+      <c r="C41" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A41,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Oracle Red Bull Racing</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A42,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Red Bull Racing-Honda RBPT</v>
+      </c>
+      <c r="C42" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A42,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Oracle Red Bull Racing</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A43,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Williams-Mercedes</v>
+      </c>
+      <c r="C43" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A43,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Williams Racing</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A44,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Williams-Mercedes</v>
+      </c>
+      <c r="C44" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A44,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
+        <v>Williams Racing</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BE0D22-4AED-4FA9-9F75-8A10C02E241C}">
+  <dimension ref="A1:AA21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="26" width="5.6640625" style="4" customWidth="1"/>
+    <col min="27" max="27" width="8.88671875" style="4"/>
+    <col min="28" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="129" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA1" s="6"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Alpine-Renault</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Alpine-Renault</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Aston Martin Aramco-Mercedes</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Aston Martin Aramco-Mercedes</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Ferrari</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Ferrari</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Haas-Ferrari</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Haas-Ferrari</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Kick Sauber-Ferrari</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Kick Sauber-Ferrari</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>McLaren-Mercedes</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>McLaren-Mercedes</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Mercedes</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Mercedes</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Racing Bulls-Honda RBPT</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Racing Bulls-Honda RBPT</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Red Bull Racing-Honda RBPT</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Red Bull Racing-Honda RBPT</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Williams-Mercedes</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="14" t="str">
+        <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
+        <v>Williams-Mercedes</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C050472A-9925-4137-B5F7-198FBD97FF72}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4219,1059 +9388,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055D11F0-CC47-46EC-A6D6-C461ECA1696D}">
-  <dimension ref="A1:AA44"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.6640625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" s="13" customFormat="1" ht="130.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="T1" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="U1" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="V1" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="W1" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="X1" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y1" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z1" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA1" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" s="13" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA2" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Alpine-Renault</v>
-      </c>
-      <c r="C3" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>BWT Alpine Formula One Team</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Alpine-Renault</v>
-      </c>
-      <c r="C4" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>BWT Alpine Formula One Team</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Aston Martin Aramco-Mercedes</v>
-      </c>
-      <c r="C5" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Aston Martin Aramco Formula One Team</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Aston Martin Aramco-Mercedes</v>
-      </c>
-      <c r="C6" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Aston Martin Aramco Formula One Team</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Ferrari</v>
-      </c>
-      <c r="C7" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Scuderia Ferrari HP</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Ferrari</v>
-      </c>
-      <c r="C8" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Scuderia Ferrari HP</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Haas-Ferrari</v>
-      </c>
-      <c r="C9" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>MoneyGram Haas F1 Team</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Haas-Ferrari</v>
-      </c>
-      <c r="C10" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>MoneyGram Haas F1 Team</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Kick Sauber-Ferrari</v>
-      </c>
-      <c r="C11" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Stake F1 Team Kick Sauber</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Kick Sauber-Ferrari</v>
-      </c>
-      <c r="C12" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Stake F1 Team Kick Sauber</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>McLaren-Mercedes</v>
-      </c>
-      <c r="C13" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>McLaren Formula 1 Team</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>McLaren-Mercedes</v>
-      </c>
-      <c r="C14" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>McLaren Formula 1 Team</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Mercedes</v>
-      </c>
-      <c r="C15" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Mercedes-AMG Petronas Formula One Team</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Mercedes</v>
-      </c>
-      <c r="C16" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Mercedes-AMG Petronas Formula One Team</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Racing Bulls-Honda RBPT</v>
-      </c>
-      <c r="C17" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Visa Cash App Racing Bulls Formula One Team</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Racing Bulls-Honda RBPT</v>
-      </c>
-      <c r="C18" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Visa Cash App Racing Bulls Formula One Team</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Red Bull Racing-Honda RBPT</v>
-      </c>
-      <c r="C19" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Oracle Red Bull Racing</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Red Bull Racing-Honda RBPT</v>
-      </c>
-      <c r="C20" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Oracle Red Bull Racing</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Williams-Mercedes</v>
-      </c>
-      <c r="C21" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Williams Racing</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Williams-Mercedes</v>
-      </c>
-      <c r="C22" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Williams Racing</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="D24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="N24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="O24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="P24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="R24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="S24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="T24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="U24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="V24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="W24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="X24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z24" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA24" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A25,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Alpine-Renault</v>
-      </c>
-      <c r="C25" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A25,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>BWT Alpine Formula One Team</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A26,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Alpine-Renault</v>
-      </c>
-      <c r="C26" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A26,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>BWT Alpine Formula One Team</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A27,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Aston Martin Aramco-Mercedes</v>
-      </c>
-      <c r="C27" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A27,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Aston Martin Aramco Formula One Team</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A28,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Aston Martin Aramco-Mercedes</v>
-      </c>
-      <c r="C28" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A28,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Aston Martin Aramco Formula One Team</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A29,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Ferrari</v>
-      </c>
-      <c r="C29" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A29,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Scuderia Ferrari HP</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A30,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Ferrari</v>
-      </c>
-      <c r="C30" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A30,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Scuderia Ferrari HP</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A31,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Haas-Ferrari</v>
-      </c>
-      <c r="C31" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A31,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>MoneyGram Haas F1 Team</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A32,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Haas-Ferrari</v>
-      </c>
-      <c r="C32" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A32,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>MoneyGram Haas F1 Team</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A33,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Kick Sauber-Ferrari</v>
-      </c>
-      <c r="C33" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A33,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Stake F1 Team Kick Sauber</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A34,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Kick Sauber-Ferrari</v>
-      </c>
-      <c r="C34" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A34,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Stake F1 Team Kick Sauber</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A35,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>McLaren-Mercedes</v>
-      </c>
-      <c r="C35" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A35,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>McLaren Formula 1 Team</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A36,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>McLaren-Mercedes</v>
-      </c>
-      <c r="C36" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A36,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>McLaren Formula 1 Team</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A37,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Mercedes</v>
-      </c>
-      <c r="C37" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A37,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Mercedes-AMG Petronas Formula One Team</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A38,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Mercedes</v>
-      </c>
-      <c r="C38" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A38,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Mercedes-AMG Petronas Formula One Team</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A39,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Racing Bulls-Honda RBPT</v>
-      </c>
-      <c r="C39" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A39,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Visa Cash App Racing Bulls Formula One Team</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A40,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Racing Bulls-Honda RBPT</v>
-      </c>
-      <c r="C40" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A40,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Visa Cash App Racing Bulls Formula One Team</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A41,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Red Bull Racing-Honda RBPT</v>
-      </c>
-      <c r="C41" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A41,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Oracle Red Bull Racing</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A42,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Red Bull Racing-Honda RBPT</v>
-      </c>
-      <c r="C42" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A42,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Oracle Red Bull Racing</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A43,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Williams-Mercedes</v>
-      </c>
-      <c r="C43" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A43,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Williams Racing</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A44,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Williams-Mercedes</v>
-      </c>
-      <c r="C44" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A44,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
-        <v>Williams Racing</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BE0D22-4AED-4FA9-9F75-8A10C02E241C}">
-  <dimension ref="A1:AA21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="26" width="5.6640625" style="4" customWidth="1"/>
-    <col min="27" max="27" width="8.88671875" style="4"/>
-    <col min="28" max="16384" width="8.88671875" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" ht="130.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA1" s="6"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Alpine-Renault</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Alpine-Renault</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Aston Martin Aramco-Mercedes</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Aston Martin Aramco-Mercedes</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Ferrari</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Ferrari</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Haas-Ferrari</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Haas-Ferrari</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Kick Sauber-Ferrari</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Kick Sauber-Ferrari</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>McLaren-Mercedes</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>McLaren-Mercedes</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Mercedes</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Mercedes</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Racing Bulls-Honda RBPT</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Racing Bulls-Honda RBPT</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Red Bull Racing-Honda RBPT</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Red Bull Racing-Honda RBPT</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Williams-Mercedes</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="14" t="str">
-        <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</f>
-        <v>Williams-Mercedes</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/data/Formula_1/Formula_1.xlsx
+++ b/data/Formula_1/Formula_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vyan\Documents\GitHub\Formula_1\data\Formula_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF2CF6C-860C-47AA-8587-92CB5E7B2540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B764D7-8CD0-40F3-A58D-C82C0989F7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Drivers" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="Constructor_Log" sheetId="5" r:id="rId5"/>
     <sheet name="Constructor" sheetId="4" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="193">
   <si>
     <t>Name</t>
   </si>
@@ -550,475 +547,79 @@
     <t>Now your table is fully detailed! Let me know if you need any tweaks.</t>
   </si>
   <si>
-    <t>1:16.315</t>
-  </si>
-  <si>
-    <t>1:32.575</t>
-  </si>
-  <si>
-    <t>1:28.877</t>
-  </si>
-  <si>
-    <t>1:31.414</t>
-  </si>
-  <si>
-    <t>1:28.739</t>
-  </si>
-  <si>
-    <t>1:29.171</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>1:16.328</t>
-  </si>
-  <si>
-    <t>1:32.640</t>
-  </si>
-  <si>
-    <t>1:28.186</t>
-  </si>
-  <si>
-    <t>1:31.462</t>
-  </si>
-  <si>
-    <t>1:28.421</t>
-  </si>
-  <si>
-    <t>1:28.345</t>
-  </si>
-  <si>
-    <t>1:15.937</t>
-  </si>
-  <si>
-    <t>1:11.994</t>
-  </si>
-  <si>
-    <t>1:16.288</t>
-  </si>
-  <si>
-    <t>1:32.121</t>
-  </si>
-  <si>
-    <t>1:28.337</t>
-  </si>
-  <si>
-    <t>1:31.634</t>
-  </si>
-  <si>
-    <t>1:28.548</t>
-  </si>
-  <si>
-    <t>1:28.455</t>
-  </si>
-  <si>
-    <t>1:15.695</t>
-  </si>
-  <si>
-    <t>1:11.674</t>
-  </si>
-  <si>
-    <t>1:16.369</t>
-  </si>
-  <si>
-    <t>1:32.327</t>
-  </si>
-  <si>
-    <t>1:29.271</t>
-  </si>
-  <si>
-    <t>1:32.283</t>
-  </si>
-  <si>
-    <t>1:28.645</t>
-  </si>
-  <si>
-    <t>1:29.028</t>
-  </si>
-  <si>
-    <t>1:15.817</t>
-  </si>
-  <si>
-    <t>1:12.563</t>
-  </si>
-  <si>
-    <t>1:16.029</t>
-  </si>
-  <si>
-    <t>1:31.518</t>
-  </si>
-  <si>
-    <t>1:27.920</t>
-  </si>
-  <si>
-    <t>1:31.454</t>
-  </si>
-  <si>
-    <t>1:28.552</t>
-  </si>
-  <si>
-    <t>1:28.325</t>
-  </si>
-  <si>
-    <t>1:16.108</t>
-  </si>
-  <si>
-    <t>1:11.229</t>
-  </si>
-  <si>
-    <t>1:16.213</t>
-  </si>
-  <si>
-    <t>1:31.212</t>
-  </si>
-  <si>
-    <t>1:27.942</t>
-  </si>
-  <si>
-    <t>1:31.219</t>
-  </si>
-  <si>
-    <t>1:28.372</t>
-  </si>
-  <si>
-    <t>1:28.231</t>
-  </si>
-  <si>
-    <t>1:16.163</t>
-  </si>
-  <si>
-    <t>1:11.575</t>
-  </si>
-  <si>
-    <t>1:17.174</t>
-  </si>
-  <si>
-    <t>1:32.651</t>
-  </si>
-  <si>
-    <t>1:28.696</t>
-  </si>
-  <si>
-    <t>1:31.594</t>
-  </si>
-  <si>
-    <t>1:29.092</t>
-  </si>
-  <si>
-    <t>1:28.303</t>
-  </si>
-  <si>
-    <t>1:16.613</t>
-  </si>
-  <si>
-    <t>1:11.839</t>
-  </si>
-  <si>
-    <t>No time</t>
-  </si>
-  <si>
-    <t>1:32.269</t>
-  </si>
-  <si>
-    <t>1:28.228</t>
-  </si>
-  <si>
-    <t>1:32.373</t>
-  </si>
-  <si>
-    <t>1:28.536</t>
-  </si>
-  <si>
-    <t>1:29.825</t>
-  </si>
-  <si>
-    <t>1:16.918</t>
-  </si>
-  <si>
-    <t>1:11.979</t>
-  </si>
-  <si>
-    <t>1:16.516</t>
-  </si>
-  <si>
-    <t>1:32.539</t>
-  </si>
-  <si>
-    <t>1:28.622</t>
-  </si>
-  <si>
-    <t>1:32.186</t>
-  </si>
-  <si>
-    <t>1:29.462</t>
-  </si>
-  <si>
-    <t>1:29.312</t>
-  </si>
-  <si>
-    <t>1:16.340</t>
-  </si>
-  <si>
-    <t>1:11.902</t>
-  </si>
-  <si>
-    <t>1:16.579</t>
-  </si>
-  <si>
-    <t>1:32.675</t>
-  </si>
-  <si>
-    <t>1:28.570</t>
-  </si>
-  <si>
-    <t>1:32.067</t>
-  </si>
-  <si>
-    <t>1:28.782</t>
-  </si>
-  <si>
-    <t>1:28.542</t>
-  </si>
-  <si>
-    <t>1:16.518</t>
-  </si>
-  <si>
-    <t>1:11.871</t>
-  </si>
-  <si>
-    <t>1:15.912</t>
-  </si>
-  <si>
-    <t>1:31.396</t>
-  </si>
-  <si>
-    <t>1:27.845</t>
-  </si>
-  <si>
-    <t>1:31.107</t>
-  </si>
-  <si>
-    <t>1:27.805</t>
-  </si>
-  <si>
-    <t>1:27.890</t>
-  </si>
-  <si>
-    <t>1:15.894</t>
-  </si>
-  <si>
-    <t>1:11.285</t>
-  </si>
-  <si>
-    <t>1:16.062</t>
-  </si>
-  <si>
-    <t>1:31.723</t>
-  </si>
-  <si>
-    <t>1:27.687</t>
-  </si>
-  <si>
-    <t>1:31.392</t>
-  </si>
-  <si>
-    <t>1:27.901</t>
-  </si>
-  <si>
-    <t>1:27.951</t>
-  </si>
-  <si>
-    <t>1:15.500</t>
-  </si>
-  <si>
-    <t>1:11.308</t>
-  </si>
-  <si>
-    <t>1:16.525</t>
-  </si>
-  <si>
-    <t>1:31.999</t>
-  </si>
-  <si>
-    <t>1:27.968</t>
-  </si>
-  <si>
-    <t>1:31.415</t>
-  </si>
-  <si>
-    <t>1:28.128</t>
-  </si>
-  <si>
-    <t>1:27.858</t>
-  </si>
-  <si>
-    <t>1:15.943</t>
-  </si>
-  <si>
-    <t>1:11.880</t>
-  </si>
-  <si>
-    <t>1:15.971</t>
-  </si>
-  <si>
-    <t>1:31.952</t>
-  </si>
-  <si>
-    <t>1:27.843</t>
-  </si>
-  <si>
-    <t>1:31.494</t>
-  </si>
-  <si>
-    <t>1:28.282</t>
-  </si>
-  <si>
-    <t>1:27.688</t>
-  </si>
-  <si>
-    <t>1:15.852</t>
-  </si>
-  <si>
-    <t>1:11.507</t>
-  </si>
-  <si>
-    <t>1:16.354</t>
-  </si>
-  <si>
-    <t>1:32.171</t>
-  </si>
-  <si>
-    <t>1:28.278</t>
-  </si>
-  <si>
-    <t>1:31.591</t>
-  </si>
-  <si>
-    <t>1:28.571</t>
-  </si>
-  <si>
-    <t>1:28.394</t>
-  </si>
-  <si>
-    <t>1:16.253</t>
-  </si>
-  <si>
-    <t>1:11.811</t>
-  </si>
-  <si>
-    <t>1:16.225</t>
-  </si>
-  <si>
-    <t>1:32.316</t>
-  </si>
-  <si>
-    <t>1:27.967</t>
-  </si>
-  <si>
-    <t>1:31.751</t>
-  </si>
-  <si>
-    <t>1:28.226</t>
-  </si>
-  <si>
-    <t>1:29.246</t>
-  </si>
-  <si>
-    <t>1:11.800</t>
-  </si>
-  <si>
-    <t>1:16.018</t>
-  </si>
-  <si>
-    <t>1:31.916</t>
-  </si>
-  <si>
-    <t>1:27.943</t>
-  </si>
-  <si>
-    <t>1:31.303</t>
-  </si>
-  <si>
-    <t>1:27.778</t>
-  </si>
-  <si>
-    <t>1:27.953</t>
-  </si>
-  <si>
-    <t>1:15.175</t>
-  </si>
-  <si>
-    <t>1:11.431</t>
-  </si>
-  <si>
-    <t>1:17.094</t>
-  </si>
-  <si>
-    <t>1:32.729</t>
-  </si>
-  <si>
-    <t>1:28.554</t>
-  </si>
-  <si>
-    <t>1:32.165</t>
-  </si>
-  <si>
-    <t>1:28.561</t>
-  </si>
-  <si>
-    <t>1:28.914</t>
-  </si>
-  <si>
-    <t>1:16.379</t>
-  </si>
-  <si>
-    <t>1:11.818</t>
-  </si>
-  <si>
-    <t>1:16.245</t>
-  </si>
-  <si>
-    <t>1:32.462</t>
-  </si>
-  <si>
-    <t>1:28.218</t>
-  </si>
-  <si>
-    <t>1:32.040</t>
-  </si>
-  <si>
-    <t>1:28.279</t>
-  </si>
-  <si>
-    <t>1:27.859</t>
-  </si>
-  <si>
-    <t>1:16.123</t>
-  </si>
-  <si>
-    <t>1:11.629</t>
-  </si>
-  <si>
-    <t>1:16.360</t>
-  </si>
-  <si>
-    <t>1:32.457</t>
-  </si>
-  <si>
-    <t>1:28.209</t>
-  </si>
-  <si>
-    <t>1:28.354</t>
-  </si>
-  <si>
-    <t>1:27.899</t>
-  </si>
-  <si>
-    <t>1:15.987</t>
-  </si>
-  <si>
-    <t>1:11.707</t>
+    <t>14</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>—1</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Ret</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>DNS1</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>DSQ</t>
+  </si>
+  <si>
+    <t>—5</t>
+  </si>
+  <si>
+    <t>DNS5</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1170,7 +771,6 @@
     <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="47" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1180,16 +780,70 @@
   </cellStyles>
   <dxfs count="109">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2170,46 +1824,231 @@
           <bgColor theme="1" tint="0.14999847407452621"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2234,239 +2073,92 @@
           <bgColor theme="1" tint="0.14999847407452621"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2491,44 +2183,25 @@
           <bgColor theme="1" tint="0.14999847407452621"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2584,79 +2257,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2668,1585 +2268,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="qualifying"/>
-      <sheetName val="Australian_Grand_Prix"/>
-      <sheetName val="Chinese_Grand_Prix"/>
-      <sheetName val="Japanese_Grand_Prix"/>
-      <sheetName val="Bahrain_Grand_Prix"/>
-      <sheetName val="Saudi_Arabian_Grand_Prix"/>
-      <sheetName val="Miami_Grand_Prix"/>
-      <sheetName val="Emilia_Romagna_Grand_Prix"/>
-      <sheetName val="Monaco_Grand_Prix"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="24">
-          <cell r="J24" t="str">
-            <v>1</v>
-          </cell>
-          <cell r="L24" t="str">
-            <v>Lando Norris</v>
-          </cell>
-          <cell r="P24" t="str">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="J25" t="str">
-            <v>2</v>
-          </cell>
-          <cell r="L25" t="str">
-            <v>Max Verstappen</v>
-          </cell>
-          <cell r="P25" t="str">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="J26" t="str">
-            <v>3</v>
-          </cell>
-          <cell r="L26" t="str">
-            <v>George Russell</v>
-          </cell>
-          <cell r="P26" t="str">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="J27" t="str">
-            <v>4</v>
-          </cell>
-          <cell r="L27" t="str">
-            <v>Andrea Kimi Antonelli</v>
-          </cell>
-          <cell r="P27" t="str">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="J28" t="str">
-            <v>5</v>
-          </cell>
-          <cell r="L28" t="str">
-            <v>Alexander Albon</v>
-          </cell>
-          <cell r="P28" t="str">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="J29" t="str">
-            <v>6</v>
-          </cell>
-          <cell r="L29" t="str">
-            <v>Lance Stroll</v>
-          </cell>
-          <cell r="P29" t="str">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="J30" t="str">
-            <v>7</v>
-          </cell>
-          <cell r="L30" t="str">
-            <v>Nico Hülkenberg</v>
-          </cell>
-          <cell r="P30" t="str">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="J31" t="str">
-            <v>8</v>
-          </cell>
-          <cell r="L31" t="str">
-            <v>Charles Leclerc</v>
-          </cell>
-          <cell r="P31" t="str">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="J32" t="str">
-            <v>9</v>
-          </cell>
-          <cell r="L32" t="str">
-            <v>Oscar Piastri</v>
-          </cell>
-          <cell r="P32" t="str">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="J33" t="str">
-            <v>10</v>
-          </cell>
-          <cell r="L33" t="str">
-            <v>Lewis Hamilton</v>
-          </cell>
-          <cell r="P33" t="str">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="J34" t="str">
-            <v>11</v>
-          </cell>
-          <cell r="L34" t="str">
-            <v>Pierre Gasly</v>
-          </cell>
-          <cell r="P34" t="str">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35" t="str">
-            <v>12</v>
-          </cell>
-          <cell r="L35" t="str">
-            <v>Yuki Tsunoda</v>
-          </cell>
-          <cell r="P35" t="str">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="J36" t="str">
-            <v>13</v>
-          </cell>
-          <cell r="L36" t="str">
-            <v>Esteban Ocon</v>
-          </cell>
-          <cell r="P36" t="str">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37" t="str">
-            <v>14</v>
-          </cell>
-          <cell r="L37" t="str">
-            <v>Oliver Bearman</v>
-          </cell>
-          <cell r="P37" t="str">
-            <v>PL</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="J38" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L38" t="str">
-            <v>Liam Lawson</v>
-          </cell>
-          <cell r="P38" t="str">
-            <v>PL</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L39" t="str">
-            <v>Gabriel Bortoleto</v>
-          </cell>
-          <cell r="P39" t="str">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="J40" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L40" t="str">
-            <v>Fernando Alonso</v>
-          </cell>
-          <cell r="P40" t="str">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v>Carlos Sainz Jr.</v>
-          </cell>
-          <cell r="P41" t="str">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="J42" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L42" t="str">
-            <v>Jack Doohan</v>
-          </cell>
-          <cell r="P42" t="str">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43" t="str">
-            <v>DNS1</v>
-          </cell>
-          <cell r="L43" t="str">
-            <v>Isack Hadjar</v>
-          </cell>
-          <cell r="P43" t="str">
-            <v>—1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="24">
-          <cell r="J24" t="str">
-            <v>1</v>
-          </cell>
-          <cell r="L24" t="str">
-            <v>Lewis Hamilton</v>
-          </cell>
-          <cell r="P24" t="str">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="J25" t="str">
-            <v>2</v>
-          </cell>
-          <cell r="L25" t="str">
-            <v>Oscar Piastri</v>
-          </cell>
-          <cell r="P25" t="str">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="J26" t="str">
-            <v>3</v>
-          </cell>
-          <cell r="L26" t="str">
-            <v>Max Verstappen</v>
-          </cell>
-          <cell r="P26" t="str">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="J27" t="str">
-            <v>4</v>
-          </cell>
-          <cell r="L27" t="str">
-            <v>George Russell</v>
-          </cell>
-          <cell r="P27" t="str">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="J28" t="str">
-            <v>5</v>
-          </cell>
-          <cell r="L28" t="str">
-            <v>Charles Leclerc</v>
-          </cell>
-          <cell r="P28" t="str">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="J29" t="str">
-            <v>6</v>
-          </cell>
-          <cell r="L29" t="str">
-            <v>Yuki Tsunoda</v>
-          </cell>
-          <cell r="P29" t="str">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="J30" t="str">
-            <v>7</v>
-          </cell>
-          <cell r="L30" t="str">
-            <v>Andrea Kimi Antonelli</v>
-          </cell>
-          <cell r="P30" t="str">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="J31" t="str">
-            <v>8</v>
-          </cell>
-          <cell r="L31" t="str">
-            <v>Lando Norris</v>
-          </cell>
-          <cell r="P31" t="str">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="J32" t="str">
-            <v>9</v>
-          </cell>
-          <cell r="L32" t="str">
-            <v>Lance Stroll</v>
-          </cell>
-          <cell r="P32" t="str">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="J33" t="str">
-            <v>10</v>
-          </cell>
-          <cell r="L33" t="str">
-            <v>Fernando Alonso</v>
-          </cell>
-          <cell r="P33" t="str">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="J34" t="str">
-            <v>11</v>
-          </cell>
-          <cell r="L34" t="str">
-            <v>Alexander Albon</v>
-          </cell>
-          <cell r="P34" t="str">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35" t="str">
-            <v>12</v>
-          </cell>
-          <cell r="L35" t="str">
-            <v>Pierre Gasly</v>
-          </cell>
-          <cell r="P35" t="str">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="J36" t="str">
-            <v>13</v>
-          </cell>
-          <cell r="L36" t="str">
-            <v>Isack Hadjar</v>
-          </cell>
-          <cell r="P36" t="str">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37" t="str">
-            <v>14</v>
-          </cell>
-          <cell r="L37" t="str">
-            <v>Liam Lawson</v>
-          </cell>
-          <cell r="P37" t="str">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="J38" t="str">
-            <v>15</v>
-          </cell>
-          <cell r="L38" t="str">
-            <v>Oliver Bearman</v>
-          </cell>
-          <cell r="P38" t="str">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39" t="str">
-            <v>16</v>
-          </cell>
-          <cell r="L39" t="str">
-            <v>Esteban Ocon</v>
-          </cell>
-          <cell r="P39" t="str">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="J40" t="str">
-            <v>17</v>
-          </cell>
-          <cell r="L40" t="str">
-            <v>Carlos Sainz Jr.</v>
-          </cell>
-          <cell r="P40" t="str">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41" t="str">
-            <v>18</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v>Gabriel Bortoleto</v>
-          </cell>
-          <cell r="P41" t="str">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="J42" t="str">
-            <v>19</v>
-          </cell>
-          <cell r="L42" t="str">
-            <v>Nico Hülkenberg</v>
-          </cell>
-          <cell r="P42" t="str">
-            <v>PL</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43" t="str">
-            <v>20</v>
-          </cell>
-          <cell r="L43" t="str">
-            <v>Jack Doohan</v>
-          </cell>
-          <cell r="P43" t="str">
-            <v>16</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="24">
-          <cell r="J24" t="str">
-            <v>1</v>
-          </cell>
-          <cell r="L24" t="str">
-            <v>Max Verstappen</v>
-          </cell>
-          <cell r="P24" t="str">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="J25" t="str">
-            <v>2</v>
-          </cell>
-          <cell r="L25" t="str">
-            <v>Lando Norris</v>
-          </cell>
-          <cell r="P25" t="str">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="J26" t="str">
-            <v>3</v>
-          </cell>
-          <cell r="L26" t="str">
-            <v>Oscar Piastri</v>
-          </cell>
-          <cell r="P26" t="str">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="J27" t="str">
-            <v>4</v>
-          </cell>
-          <cell r="L27" t="str">
-            <v>Charles Leclerc</v>
-          </cell>
-          <cell r="P27" t="str">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="J28" t="str">
-            <v>5</v>
-          </cell>
-          <cell r="L28" t="str">
-            <v>George Russell</v>
-          </cell>
-          <cell r="P28" t="str">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="J29" t="str">
-            <v>6</v>
-          </cell>
-          <cell r="L29" t="str">
-            <v>Andrea Kimi Antonelli</v>
-          </cell>
-          <cell r="P29" t="str">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="J30" t="str">
-            <v>7</v>
-          </cell>
-          <cell r="L30" t="str">
-            <v>Lewis Hamilton</v>
-          </cell>
-          <cell r="P30" t="str">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="J31" t="str">
-            <v>8</v>
-          </cell>
-          <cell r="L31" t="str">
-            <v>Isack Hadjar</v>
-          </cell>
-          <cell r="P31" t="str">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="J32" t="str">
-            <v>9</v>
-          </cell>
-          <cell r="L32" t="str">
-            <v>Alexander Albon</v>
-          </cell>
-          <cell r="P32" t="str">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="J33" t="str">
-            <v>10</v>
-          </cell>
-          <cell r="L33" t="str">
-            <v>Oliver Bearman</v>
-          </cell>
-          <cell r="P33" t="str">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="J34" t="str">
-            <v>11</v>
-          </cell>
-          <cell r="L34" t="str">
-            <v>Fernando Alonso</v>
-          </cell>
-          <cell r="P34" t="str">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35" t="str">
-            <v>12</v>
-          </cell>
-          <cell r="L35" t="str">
-            <v>Yuki Tsunoda</v>
-          </cell>
-          <cell r="P35" t="str">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="J36" t="str">
-            <v>13</v>
-          </cell>
-          <cell r="L36" t="str">
-            <v>Pierre Gasly</v>
-          </cell>
-          <cell r="P36" t="str">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37" t="str">
-            <v>14</v>
-          </cell>
-          <cell r="L37" t="str">
-            <v>Carlos Sainz Jr.</v>
-          </cell>
-          <cell r="P37" t="str">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="J38" t="str">
-            <v>15</v>
-          </cell>
-          <cell r="L38" t="str">
-            <v>Jack Doohan</v>
-          </cell>
-          <cell r="P38" t="str">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39" t="str">
-            <v>16</v>
-          </cell>
-          <cell r="L39" t="str">
-            <v>Nico Hülkenberg</v>
-          </cell>
-          <cell r="P39" t="str">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="J40" t="str">
-            <v>17</v>
-          </cell>
-          <cell r="L40" t="str">
-            <v>Liam Lawson</v>
-          </cell>
-          <cell r="P40" t="str">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41" t="str">
-            <v>18</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v>Esteban Ocon</v>
-          </cell>
-          <cell r="P41" t="str">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="J42" t="str">
-            <v>19</v>
-          </cell>
-          <cell r="L42" t="str">
-            <v>Gabriel Bortoleto</v>
-          </cell>
-          <cell r="P42" t="str">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43" t="str">
-            <v>20</v>
-          </cell>
-          <cell r="L43" t="str">
-            <v>Lance Stroll</v>
-          </cell>
-          <cell r="P43" t="str">
-            <v>20</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="24">
-          <cell r="J24" t="str">
-            <v>1</v>
-          </cell>
-          <cell r="L24" t="str">
-            <v>Oscar Piastri</v>
-          </cell>
-          <cell r="P24" t="str">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="J25" t="str">
-            <v>2</v>
-          </cell>
-          <cell r="L25" t="str">
-            <v>George Russell</v>
-          </cell>
-          <cell r="P25" t="str">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="J26" t="str">
-            <v>3</v>
-          </cell>
-          <cell r="L26" t="str">
-            <v>Lando Norris</v>
-          </cell>
-          <cell r="P26" t="str">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="J27" t="str">
-            <v>4</v>
-          </cell>
-          <cell r="L27" t="str">
-            <v>Charles Leclerc</v>
-          </cell>
-          <cell r="P27" t="str">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="J28" t="str">
-            <v>5</v>
-          </cell>
-          <cell r="L28" t="str">
-            <v>Lewis Hamilton</v>
-          </cell>
-          <cell r="P28" t="str">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="J29" t="str">
-            <v>6</v>
-          </cell>
-          <cell r="L29" t="str">
-            <v>Max Verstappen</v>
-          </cell>
-          <cell r="P29" t="str">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="J30" t="str">
-            <v>7</v>
-          </cell>
-          <cell r="L30" t="str">
-            <v>Pierre Gasly</v>
-          </cell>
-          <cell r="P30" t="str">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="J31" t="str">
-            <v>8</v>
-          </cell>
-          <cell r="L31" t="str">
-            <v>Esteban Ocon</v>
-          </cell>
-          <cell r="P31" t="str">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="J32" t="str">
-            <v>9</v>
-          </cell>
-          <cell r="L32" t="str">
-            <v>Yuki Tsunoda</v>
-          </cell>
-          <cell r="P32" t="str">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="J33" t="str">
-            <v>10</v>
-          </cell>
-          <cell r="L33" t="str">
-            <v>Oliver Bearman</v>
-          </cell>
-          <cell r="P33" t="str">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="J34" t="str">
-            <v>11</v>
-          </cell>
-          <cell r="L34" t="str">
-            <v>Andrea Kimi Antonelli</v>
-          </cell>
-          <cell r="P34" t="str">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35" t="str">
-            <v>12</v>
-          </cell>
-          <cell r="L35" t="str">
-            <v>Alexander Albon</v>
-          </cell>
-          <cell r="P35" t="str">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="J36" t="str">
-            <v>13</v>
-          </cell>
-          <cell r="L36" t="str">
-            <v>Isack Hadjar</v>
-          </cell>
-          <cell r="P36" t="str">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37" t="str">
-            <v>14</v>
-          </cell>
-          <cell r="L37" t="str">
-            <v>Jack Doohan</v>
-          </cell>
-          <cell r="P37" t="str">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="J38" t="str">
-            <v>15</v>
-          </cell>
-          <cell r="L38" t="str">
-            <v>Fernando Alonso</v>
-          </cell>
-          <cell r="P38" t="str">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39" t="str">
-            <v>16</v>
-          </cell>
-          <cell r="L39" t="str">
-            <v>Liam Lawson</v>
-          </cell>
-          <cell r="P39" t="str">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="J40" t="str">
-            <v>17</v>
-          </cell>
-          <cell r="L40" t="str">
-            <v>Lance Stroll</v>
-          </cell>
-          <cell r="P40" t="str">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41" t="str">
-            <v>18</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v>Gabriel Bortoleto</v>
-          </cell>
-          <cell r="P41" t="str">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="J42" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L42" t="str">
-            <v>Carlos Sainz Jr.</v>
-          </cell>
-          <cell r="P42" t="str">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43" t="str">
-            <v>DSQ</v>
-          </cell>
-          <cell r="L43" t="str">
-            <v>Nico Hülkenberg</v>
-          </cell>
-          <cell r="P43" t="str">
-            <v>16</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="24">
-          <cell r="J24" t="str">
-            <v>1</v>
-          </cell>
-          <cell r="L24" t="str">
-            <v>Oscar Piastri</v>
-          </cell>
-          <cell r="P24" t="str">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="J25" t="str">
-            <v>2</v>
-          </cell>
-          <cell r="L25" t="str">
-            <v>Max Verstappen</v>
-          </cell>
-          <cell r="P25" t="str">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="J26" t="str">
-            <v>3</v>
-          </cell>
-          <cell r="L26" t="str">
-            <v>Charles Leclerc</v>
-          </cell>
-          <cell r="P26" t="str">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="J27" t="str">
-            <v>4</v>
-          </cell>
-          <cell r="L27" t="str">
-            <v>Lando Norris</v>
-          </cell>
-          <cell r="P27" t="str">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="J28" t="str">
-            <v>5</v>
-          </cell>
-          <cell r="L28" t="str">
-            <v>George Russell</v>
-          </cell>
-          <cell r="P28" t="str">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="J29" t="str">
-            <v>6</v>
-          </cell>
-          <cell r="L29" t="str">
-            <v>Andrea Kimi Antonelli</v>
-          </cell>
-          <cell r="P29" t="str">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="J30" t="str">
-            <v>7</v>
-          </cell>
-          <cell r="L30" t="str">
-            <v>Lewis Hamilton</v>
-          </cell>
-          <cell r="P30" t="str">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="J31" t="str">
-            <v>8</v>
-          </cell>
-          <cell r="L31" t="str">
-            <v>Carlos Sainz Jr.</v>
-          </cell>
-          <cell r="P31" t="str">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="J32" t="str">
-            <v>9</v>
-          </cell>
-          <cell r="L32" t="str">
-            <v>Alexander Albon</v>
-          </cell>
-          <cell r="P32" t="str">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="J33" t="str">
-            <v>10</v>
-          </cell>
-          <cell r="L33" t="str">
-            <v>Isack Hadjar</v>
-          </cell>
-          <cell r="P33" t="str">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="J34" t="str">
-            <v>11</v>
-          </cell>
-          <cell r="L34" t="str">
-            <v>Fernando Alonso</v>
-          </cell>
-          <cell r="P34" t="str">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35" t="str">
-            <v>12</v>
-          </cell>
-          <cell r="L35" t="str">
-            <v>Liam Lawson</v>
-          </cell>
-          <cell r="P35" t="str">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="J36" t="str">
-            <v>13</v>
-          </cell>
-          <cell r="L36" t="str">
-            <v>Oliver Bearman</v>
-          </cell>
-          <cell r="P36" t="str">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37" t="str">
-            <v>14</v>
-          </cell>
-          <cell r="L37" t="str">
-            <v>Esteban Ocon</v>
-          </cell>
-          <cell r="P37" t="str">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="J38" t="str">
-            <v>15</v>
-          </cell>
-          <cell r="L38" t="str">
-            <v>Nico Hülkenberg</v>
-          </cell>
-          <cell r="P38" t="str">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39" t="str">
-            <v>16</v>
-          </cell>
-          <cell r="L39" t="str">
-            <v>Lance Stroll</v>
-          </cell>
-          <cell r="P39" t="str">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="J40" t="str">
-            <v>17</v>
-          </cell>
-          <cell r="L40" t="str">
-            <v>Jack Doohan</v>
-          </cell>
-          <cell r="P40" t="str">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41" t="str">
-            <v>18</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v>Gabriel Bortoleto</v>
-          </cell>
-          <cell r="P41" t="str">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="J42" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L42" t="str">
-            <v>Yuki Tsunoda</v>
-          </cell>
-          <cell r="P42" t="str">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L43" t="str">
-            <v>Pierre Gasly</v>
-          </cell>
-          <cell r="P43" t="str">
-            <v>9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6">
-        <row r="24">
-          <cell r="J24" t="str">
-            <v>1</v>
-          </cell>
-          <cell r="L24" t="str">
-            <v>Lando Norris</v>
-          </cell>
-          <cell r="P24">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="J25" t="str">
-            <v>2</v>
-          </cell>
-          <cell r="L25" t="str">
-            <v>Oscar Piastri</v>
-          </cell>
-          <cell r="P25" t="str">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="J26" t="str">
-            <v>3</v>
-          </cell>
-          <cell r="L26" t="str">
-            <v>Lewis Hamilton</v>
-          </cell>
-          <cell r="P26" t="str">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="J27" t="str">
-            <v>4</v>
-          </cell>
-          <cell r="L27" t="str">
-            <v>George Russell</v>
-          </cell>
-          <cell r="P27" t="str">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="J28" t="str">
-            <v>5</v>
-          </cell>
-          <cell r="L28" t="str">
-            <v>Lance Stroll</v>
-          </cell>
-          <cell r="P28" t="str">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="J29" t="str">
-            <v>6</v>
-          </cell>
-          <cell r="L29" t="str">
-            <v>Yuki Tsunoda</v>
-          </cell>
-          <cell r="P29" t="str">
-            <v>PL</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="J30" t="str">
-            <v>7</v>
-          </cell>
-          <cell r="L30" t="str">
-            <v>Andrea Kimi Antonelli</v>
-          </cell>
-          <cell r="P30" t="str">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="J31" t="str">
-            <v>8</v>
-          </cell>
-          <cell r="L31" t="str">
-            <v>Pierre Gasly</v>
-          </cell>
-          <cell r="P31" t="str">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="J32" t="str">
-            <v>9</v>
-          </cell>
-          <cell r="L32" t="str">
-            <v>Nico Hülkenberg</v>
-          </cell>
-          <cell r="P32" t="str">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="J33" t="str">
-            <v>10</v>
-          </cell>
-          <cell r="L33" t="str">
-            <v>Isack Hadjar</v>
-          </cell>
-          <cell r="P33" t="str">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="J34" t="str">
-            <v>11</v>
-          </cell>
-          <cell r="L34" t="str">
-            <v>Alexander Albon</v>
-          </cell>
-          <cell r="P34" t="str">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35" t="str">
-            <v>12</v>
-          </cell>
-          <cell r="L35" t="str">
-            <v>Esteban Ocon</v>
-          </cell>
-          <cell r="P35" t="str">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="J36" t="str">
-            <v>13</v>
-          </cell>
-          <cell r="L36" t="str">
-            <v>Liam Lawson</v>
-          </cell>
-          <cell r="P36" t="str">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37" t="str">
-            <v>14</v>
-          </cell>
-          <cell r="L37" t="str">
-            <v>Oliver Bearman</v>
-          </cell>
-          <cell r="P37" t="str">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="J38" t="str">
-            <v>15</v>
-          </cell>
-          <cell r="L38" t="str">
-            <v>Gabriel Bortoleto</v>
-          </cell>
-          <cell r="P38" t="str">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39" t="str">
-            <v>16</v>
-          </cell>
-          <cell r="L39" t="str">
-            <v>Jack Doohan</v>
-          </cell>
-          <cell r="P39" t="str">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="J40" t="str">
-            <v>17</v>
-          </cell>
-          <cell r="L40" t="str">
-            <v>Max Verstappen</v>
-          </cell>
-          <cell r="P40" t="str">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v>Fernando Alonso</v>
-          </cell>
-          <cell r="P41" t="str">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="J42" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L42" t="str">
-            <v>Carlos Sainz Jr.</v>
-          </cell>
-          <cell r="P42" t="str">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43" t="str">
-            <v>DNS5</v>
-          </cell>
-          <cell r="L43" t="str">
-            <v>Charles Leclerc</v>
-          </cell>
-          <cell r="P43" t="str">
-            <v>—5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
-        <row r="24">
-          <cell r="J24" t="str">
-            <v>1</v>
-          </cell>
-          <cell r="L24" t="str">
-            <v>Lando Norris</v>
-          </cell>
-          <cell r="P24">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="J25" t="str">
-            <v>2</v>
-          </cell>
-          <cell r="L25" t="str">
-            <v>Charles Leclerc</v>
-          </cell>
-          <cell r="P25">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="J26" t="str">
-            <v>3</v>
-          </cell>
-          <cell r="L26" t="str">
-            <v>Oscar Piastri</v>
-          </cell>
-          <cell r="P26">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="J27" t="str">
-            <v>4</v>
-          </cell>
-          <cell r="L27" t="str">
-            <v>Max Verstappen</v>
-          </cell>
-          <cell r="P27">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="J28" t="str">
-            <v>5</v>
-          </cell>
-          <cell r="L28" t="str">
-            <v>Lewis Hamilton</v>
-          </cell>
-          <cell r="P28">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="J29" t="str">
-            <v>6</v>
-          </cell>
-          <cell r="L29" t="str">
-            <v>Isack Hadjar</v>
-          </cell>
-          <cell r="P29">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="J30" t="str">
-            <v>7</v>
-          </cell>
-          <cell r="L30" t="str">
-            <v>Esteban Ocon</v>
-          </cell>
-          <cell r="P30">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="J31" t="str">
-            <v>8</v>
-          </cell>
-          <cell r="L31" t="str">
-            <v>Liam Lawson</v>
-          </cell>
-          <cell r="P31">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="J32" t="str">
-            <v>9</v>
-          </cell>
-          <cell r="L32" t="str">
-            <v>Alexander Albon</v>
-          </cell>
-          <cell r="P32">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="J33" t="str">
-            <v>10</v>
-          </cell>
-          <cell r="L33" t="str">
-            <v>Carlos Sainz Jr.</v>
-          </cell>
-          <cell r="P33">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="J34" t="str">
-            <v>11</v>
-          </cell>
-          <cell r="L34" t="str">
-            <v>George Russell</v>
-          </cell>
-          <cell r="P34">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="J35" t="str">
-            <v>12</v>
-          </cell>
-          <cell r="L35" t="str">
-            <v>Oliver Bearman</v>
-          </cell>
-          <cell r="P35">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="J36" t="str">
-            <v>13</v>
-          </cell>
-          <cell r="L36" t="str">
-            <v>Franco Colapinto</v>
-          </cell>
-          <cell r="P36">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="J37" t="str">
-            <v>14</v>
-          </cell>
-          <cell r="L37" t="str">
-            <v>Gabriel Bortoleto</v>
-          </cell>
-          <cell r="P37">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="J38" t="str">
-            <v>15</v>
-          </cell>
-          <cell r="L38" t="str">
-            <v>Lance Stroll</v>
-          </cell>
-          <cell r="P38">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="J39" t="str">
-            <v>16</v>
-          </cell>
-          <cell r="L39" t="str">
-            <v>Nico Hülkenberg</v>
-          </cell>
-          <cell r="P39">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="J40" t="str">
-            <v>17</v>
-          </cell>
-          <cell r="L40" t="str">
-            <v>Yuki Tsunoda</v>
-          </cell>
-          <cell r="P40">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="J41" t="str">
-            <v>18</v>
-          </cell>
-          <cell r="L41" t="str">
-            <v>Andrea Kimi Antonelli</v>
-          </cell>
-          <cell r="P41">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="J42" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L42" t="str">
-            <v>Fernando Alonso</v>
-          </cell>
-          <cell r="P42">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="J43" t="str">
-            <v>Ret</v>
-          </cell>
-          <cell r="L43" t="str">
-            <v>Pierre Gasly</v>
-          </cell>
-          <cell r="P43">
-            <v>17</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4271,142 +2292,140 @@
     <tableColumn id="2" xr3:uid="{A2C1729C-5A9F-4F3B-9D25-29460232C8BB}" name="Circuit Name" dataDxfId="98"/>
     <tableColumn id="3" xr3:uid="{CDE8E4A3-91F0-42E8-9535-50FE31EF16BE}" name="Location" dataDxfId="97"/>
     <tableColumn id="4" xr3:uid="{15A0D957-CB98-4793-9130-02DA6096C7EE}" name="Race Date" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{5C322528-271F-4EDD-8D7B-6FAE995790B5}" name="Distance" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E39D53C2-53BA-4179-9C6E-AD4D5427D7C5}" name="Fastest Time" dataDxfId="0">
-      <calculatedColumnFormula>[1]Australian_Grand_Prix!$O$24</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{61ABA8A6-ABC2-4008-93AA-C07FC2524B57}" name="1" dataDxfId="95"/>
-    <tableColumn id="8" xr3:uid="{91B3BA5A-8F2D-45BB-B42E-FCE1231D8296}" name="2" dataDxfId="94"/>
-    <tableColumn id="9" xr3:uid="{208C354C-D504-490A-9A6E-F1C70382A1BD}" name="3" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{5C322528-271F-4EDD-8D7B-6FAE995790B5}" name="Distance" dataDxfId="95"/>
+    <tableColumn id="6" xr3:uid="{E39D53C2-53BA-4179-9C6E-AD4D5427D7C5}" name="Fastest Time" dataDxfId="94"/>
+    <tableColumn id="7" xr3:uid="{61ABA8A6-ABC2-4008-93AA-C07FC2524B57}" name="1" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{91B3BA5A-8F2D-45BB-B42E-FCE1231D8296}" name="2" dataDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{208C354C-D504-490A-9A6E-F1C70382A1BD}" name="3" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}" name="Table4" displayName="Table4" ref="A1:Y44" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}" name="Table4" displayName="Table4" ref="A1:Y44" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
   <autoFilter ref="A1:Y44" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{CF33613A-B550-44CB-881B-6F14CACD5B72}" name="Driver" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{64862BF4-56F0-4709-A8AB-C085BAF0215A}" name="Australian Grand Prix" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{2D3377A0-58D7-467A-99BD-8DD5E5195992}" name="Chinese Grand Prix" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{0ECE7874-3069-4E86-A858-526B2561A56E}" name="Japanese Grand Prix" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{3332362F-E796-4D76-B72D-D37A9E8C4506}" name="Bahrain Grand Prix" dataDxfId="86"/>
-    <tableColumn id="7" xr3:uid="{6A873417-5AFE-4D0F-88A9-6011AD971FED}" name="Saudi Arabian Grand Prix" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{2384B2F0-E1B8-4D15-A86A-C506AC2DDE75}" name="Miami Grand Prix" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{A4F6721E-F16D-4038-BD64-3E8A7D38B02F}" name="Emilia Romagna Grand Prix" dataDxfId="83"/>
-    <tableColumn id="10" xr3:uid="{435C1CC1-7C35-4D05-B75A-E2D3EA9487F5}" name="Monaco Grand Prix" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{7324DE86-EE77-4D97-944F-558B5246B501}" name="Spanish Grand Prix" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{B0654BA4-C5FE-40FC-94D4-F2829B439C83}" name="Canadian Grand Prix" dataDxfId="80"/>
-    <tableColumn id="13" xr3:uid="{40A2DB89-A1EF-4668-BB5F-0C8F41981CE9}" name="Austrian Grand Prix" dataDxfId="79"/>
-    <tableColumn id="14" xr3:uid="{7E4C0B80-60BB-443B-B58C-2C484E838E2D}" name="British Grand Prix" dataDxfId="78"/>
-    <tableColumn id="15" xr3:uid="{D7685E94-DED7-4922-8549-80717F6854B8}" name="Belgian Grand Prix" dataDxfId="77"/>
-    <tableColumn id="16" xr3:uid="{E8B67644-354D-4320-AEE9-C7236B9F7A62}" name="Hungarian Grand Prix" dataDxfId="76"/>
-    <tableColumn id="17" xr3:uid="{9744C7B8-818D-4DE8-B37D-EFBCC20F2D87}" name="Dutch Grand Prix" dataDxfId="75"/>
-    <tableColumn id="18" xr3:uid="{EF67C45C-CAC1-4298-A58A-EEA09E9B8331}" name="Italian Grand Prix" dataDxfId="74"/>
-    <tableColumn id="19" xr3:uid="{298F9D14-379A-45B8-8779-FD50639B978E}" name="Azerbaijan Grand Prix" dataDxfId="73"/>
-    <tableColumn id="20" xr3:uid="{A88F8700-7FAE-4431-8633-EE182CD448DA}" name="Singapore Grand Prix" dataDxfId="72"/>
-    <tableColumn id="21" xr3:uid="{EDA628AE-0844-4D1C-9A31-622106A74B74}" name="United States Grand Prix" dataDxfId="71"/>
-    <tableColumn id="22" xr3:uid="{40DA2915-5603-475B-B8B3-83784AE5046E}" name="Mexico City Grand Prix" dataDxfId="70"/>
-    <tableColumn id="23" xr3:uid="{46622AFA-DB78-4AE5-89D9-F1D3556D5A3D}" name="São Paulo Grand Prix" dataDxfId="69"/>
-    <tableColumn id="24" xr3:uid="{3EC53053-E45B-44EE-AC6B-F7BB5EB7B9F5}" name="Las Vegas Grand Prix" dataDxfId="68"/>
-    <tableColumn id="25" xr3:uid="{6F3819A8-BF88-4B0C-9F74-4EE092BA245E}" name="Qatar Grand Prix" dataDxfId="67"/>
-    <tableColumn id="26" xr3:uid="{6A29A013-FF84-400E-8F74-E5A850484E6D}" name="Abu Dhabi Grand Prix" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{CF33613A-B550-44CB-881B-6F14CACD5B72}" name="Driver" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{64862BF4-56F0-4709-A8AB-C085BAF0215A}" name="Australian Grand Prix" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{2D3377A0-58D7-467A-99BD-8DD5E5195992}" name="Chinese Grand Prix" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{0ECE7874-3069-4E86-A858-526B2561A56E}" name="Japanese Grand Prix" dataDxfId="85"/>
+    <tableColumn id="6" xr3:uid="{3332362F-E796-4D76-B72D-D37A9E8C4506}" name="Bahrain Grand Prix" dataDxfId="84"/>
+    <tableColumn id="7" xr3:uid="{6A873417-5AFE-4D0F-88A9-6011AD971FED}" name="Saudi Arabian Grand Prix" dataDxfId="83"/>
+    <tableColumn id="8" xr3:uid="{2384B2F0-E1B8-4D15-A86A-C506AC2DDE75}" name="Miami Grand Prix" dataDxfId="82"/>
+    <tableColumn id="9" xr3:uid="{A4F6721E-F16D-4038-BD64-3E8A7D38B02F}" name="Emilia Romagna Grand Prix" dataDxfId="81"/>
+    <tableColumn id="10" xr3:uid="{435C1CC1-7C35-4D05-B75A-E2D3EA9487F5}" name="Monaco Grand Prix" dataDxfId="80"/>
+    <tableColumn id="11" xr3:uid="{7324DE86-EE77-4D97-944F-558B5246B501}" name="Spanish Grand Prix" dataDxfId="79"/>
+    <tableColumn id="12" xr3:uid="{B0654BA4-C5FE-40FC-94D4-F2829B439C83}" name="Canadian Grand Prix" dataDxfId="78"/>
+    <tableColumn id="13" xr3:uid="{40A2DB89-A1EF-4668-BB5F-0C8F41981CE9}" name="Austrian Grand Prix" dataDxfId="77"/>
+    <tableColumn id="14" xr3:uid="{7E4C0B80-60BB-443B-B58C-2C484E838E2D}" name="British Grand Prix" dataDxfId="76"/>
+    <tableColumn id="15" xr3:uid="{D7685E94-DED7-4922-8549-80717F6854B8}" name="Belgian Grand Prix" dataDxfId="75"/>
+    <tableColumn id="16" xr3:uid="{E8B67644-354D-4320-AEE9-C7236B9F7A62}" name="Hungarian Grand Prix" dataDxfId="74"/>
+    <tableColumn id="17" xr3:uid="{9744C7B8-818D-4DE8-B37D-EFBCC20F2D87}" name="Dutch Grand Prix" dataDxfId="73"/>
+    <tableColumn id="18" xr3:uid="{EF67C45C-CAC1-4298-A58A-EEA09E9B8331}" name="Italian Grand Prix" dataDxfId="72"/>
+    <tableColumn id="19" xr3:uid="{298F9D14-379A-45B8-8779-FD50639B978E}" name="Azerbaijan Grand Prix" dataDxfId="71"/>
+    <tableColumn id="20" xr3:uid="{A88F8700-7FAE-4431-8633-EE182CD448DA}" name="Singapore Grand Prix" dataDxfId="70"/>
+    <tableColumn id="21" xr3:uid="{EDA628AE-0844-4D1C-9A31-622106A74B74}" name="United States Grand Prix" dataDxfId="69"/>
+    <tableColumn id="22" xr3:uid="{40DA2915-5603-475B-B8B3-83784AE5046E}" name="Mexico City Grand Prix" dataDxfId="68"/>
+    <tableColumn id="23" xr3:uid="{46622AFA-DB78-4AE5-89D9-F1D3556D5A3D}" name="São Paulo Grand Prix" dataDxfId="67"/>
+    <tableColumn id="24" xr3:uid="{3EC53053-E45B-44EE-AC6B-F7BB5EB7B9F5}" name="Las Vegas Grand Prix" dataDxfId="66"/>
+    <tableColumn id="25" xr3:uid="{6F3819A8-BF88-4B0C-9F74-4EE092BA245E}" name="Qatar Grand Prix" dataDxfId="65"/>
+    <tableColumn id="26" xr3:uid="{6A29A013-FF84-400E-8F74-E5A850484E6D}" name="Abu Dhabi Grand Prix" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}" name="Table6" displayName="Table6" ref="A1:AA44" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}" name="Table6" displayName="Table6" ref="A1:AA44" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:AA44" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{E278D08B-82F0-48D0-A658-DE818A33E0B8}" name="Driver" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{00D7725B-DFFE-4C3A-ACCE-32C162A4E831}" name="Constructor" dataDxfId="55">
+    <tableColumn id="1" xr3:uid="{E278D08B-82F0-48D0-A658-DE818A33E0B8}" name="Driver" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{00D7725B-DFFE-4C3A-ACCE-32C162A4E831}" name="Constructor" dataDxfId="60">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8FDBF4AD-2961-4047-8F65-8E8ADEDC3502}" name="Team" dataDxfId="54">
+    <tableColumn id="3" xr3:uid="{8FDBF4AD-2961-4047-8F65-8E8ADEDC3502}" name="Team" dataDxfId="59">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FEF76843-A12B-4494-995B-783FB04E6013}" name="Australian Grand Prix" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{17071EA5-F41C-4EBD-94F0-1B51429AF44F}" name="Chinese Grand Prix" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{F5001349-A1D5-43C9-97E1-9460CA742B63}" name="Japanese Grand Prix" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{6D0913D3-24E1-4ACA-B912-74174373B813}" name="Bahrain Grand Prix" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{E4C84672-BC98-4DF5-B9EE-8A8055F39F2D}" name="Saudi Arabian Grand Prix" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{BB7D339C-688A-4E60-8767-047C06319E68}" name="Miami Grand Prix" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{57075CE6-6548-4845-A50E-8AEFC61753A4}" name="Emilia Romagna Grand Prix" dataDxfId="47"/>
-    <tableColumn id="11" xr3:uid="{EE6736F8-ADB5-4E71-B05F-97594B3B3472}" name="Monaco Grand Prix" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{7968AD0F-F03C-43FE-9936-B9C133C05B68}" name="Spanish Grand Prix" dataDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{B8990854-8E63-4954-BB66-C62E6A969529}" name="Canadian Grand Prix" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{0E25BBA9-F83B-4D7F-B1E2-448AE6406574}" name="Austrian Grand Prix" dataDxfId="43"/>
-    <tableColumn id="15" xr3:uid="{AFBF197F-D2AA-4D23-9095-09D50B18B3F7}" name="British Grand Prix" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{CF02CCED-BF33-4C52-A70B-20F8601C2B11}" name="Belgian Grand Prix" dataDxfId="41"/>
-    <tableColumn id="17" xr3:uid="{7104019E-E290-4E2A-85C1-75D032C22FCE}" name="Hungarian Grand Prix" dataDxfId="40"/>
-    <tableColumn id="18" xr3:uid="{FFF263A4-5EE2-49F0-9BA6-08425F3D3FE9}" name="Dutch Grand Prix" dataDxfId="39"/>
-    <tableColumn id="19" xr3:uid="{0A2EFD7F-EE8D-449A-ADD0-4CCC316EBCE8}" name="Italian Grand Prix" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{EB37AA19-112E-41AF-8572-4A071B7C2217}" name="Azerbaijan Grand Prix" dataDxfId="37"/>
-    <tableColumn id="21" xr3:uid="{E5F20E2D-66D0-473E-B944-BB69CCC67E52}" name="Singapore Grand Prix" dataDxfId="36"/>
-    <tableColumn id="22" xr3:uid="{2C2EEBC6-3F36-4C36-B283-0B40A3DEF047}" name="United States Grand Prix" dataDxfId="35"/>
-    <tableColumn id="23" xr3:uid="{F863F260-3241-4267-96F8-B19D16BA264E}" name="Mexico City Grand Prix" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{9076A145-7D0A-4875-BB6A-4FB7D295FC47}" name="São Paulo Grand Prix" dataDxfId="33"/>
-    <tableColumn id="25" xr3:uid="{E68C8DA5-1B26-4FD9-A9B3-04738D5CD8FB}" name="Las Vegas Grand Prix" dataDxfId="32"/>
-    <tableColumn id="26" xr3:uid="{149AD907-AF11-4CF7-A5B7-75B2C9170D15}" name="Qatar Grand Prix" dataDxfId="31"/>
-    <tableColumn id="27" xr3:uid="{940BCA92-8A19-4BC4-979F-FC730E0FF0D9}" name="Abu Dhabi Grand Prix" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{FEF76843-A12B-4494-995B-783FB04E6013}" name="Australian Grand Prix" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{17071EA5-F41C-4EBD-94F0-1B51429AF44F}" name="Chinese Grand Prix" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{F5001349-A1D5-43C9-97E1-9460CA742B63}" name="Japanese Grand Prix" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{6D0913D3-24E1-4ACA-B912-74174373B813}" name="Bahrain Grand Prix" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{E4C84672-BC98-4DF5-B9EE-8A8055F39F2D}" name="Saudi Arabian Grand Prix" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{BB7D339C-688A-4E60-8767-047C06319E68}" name="Miami Grand Prix" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{57075CE6-6548-4845-A50E-8AEFC61753A4}" name="Emilia Romagna Grand Prix" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{EE6736F8-ADB5-4E71-B05F-97594B3B3472}" name="Monaco Grand Prix" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{7968AD0F-F03C-43FE-9936-B9C133C05B68}" name="Spanish Grand Prix" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{B8990854-8E63-4954-BB66-C62E6A969529}" name="Canadian Grand Prix" dataDxfId="49"/>
+    <tableColumn id="14" xr3:uid="{0E25BBA9-F83B-4D7F-B1E2-448AE6406574}" name="Austrian Grand Prix" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{AFBF197F-D2AA-4D23-9095-09D50B18B3F7}" name="British Grand Prix" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{CF02CCED-BF33-4C52-A70B-20F8601C2B11}" name="Belgian Grand Prix" dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{7104019E-E290-4E2A-85C1-75D032C22FCE}" name="Hungarian Grand Prix" dataDxfId="45"/>
+    <tableColumn id="18" xr3:uid="{FFF263A4-5EE2-49F0-9BA6-08425F3D3FE9}" name="Dutch Grand Prix" dataDxfId="44"/>
+    <tableColumn id="19" xr3:uid="{0A2EFD7F-EE8D-449A-ADD0-4CCC316EBCE8}" name="Italian Grand Prix" dataDxfId="43"/>
+    <tableColumn id="20" xr3:uid="{EB37AA19-112E-41AF-8572-4A071B7C2217}" name="Azerbaijan Grand Prix" dataDxfId="42"/>
+    <tableColumn id="21" xr3:uid="{E5F20E2D-66D0-473E-B944-BB69CCC67E52}" name="Singapore Grand Prix" dataDxfId="41"/>
+    <tableColumn id="22" xr3:uid="{2C2EEBC6-3F36-4C36-B283-0B40A3DEF047}" name="United States Grand Prix" dataDxfId="40"/>
+    <tableColumn id="23" xr3:uid="{F863F260-3241-4267-96F8-B19D16BA264E}" name="Mexico City Grand Prix" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{9076A145-7D0A-4875-BB6A-4FB7D295FC47}" name="São Paulo Grand Prix" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{E68C8DA5-1B26-4FD9-A9B3-04738D5CD8FB}" name="Las Vegas Grand Prix" dataDxfId="37"/>
+    <tableColumn id="26" xr3:uid="{149AD907-AF11-4CF7-A5B7-75B2C9170D15}" name="Qatar Grand Prix" dataDxfId="36"/>
+    <tableColumn id="27" xr3:uid="{940BCA92-8A19-4BC4-979F-FC730E0FF0D9}" name="Abu Dhabi Grand Prix" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}" name="Table7" displayName="Table7" ref="A1:Z21" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}" name="Table7" displayName="Table7" ref="A1:Z21" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="A1:Z21" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{04FE50CB-43CC-4C2C-B3E5-20381A77C6EE}" name="Driver" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{6F987E8C-773F-4CD7-8683-D3D2A2357DFC}" name="Constructor" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{04FE50CB-43CC-4C2C-B3E5-20381A77C6EE}" name="Driver" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{6F987E8C-773F-4CD7-8683-D3D2A2357DFC}" name="Constructor" dataDxfId="31">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$21,Constructor!$B$2:$B$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F55A6B37-6EDE-41E4-B6B2-EE2FF245418C}" name="Australian Grand Prix" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{07D64B60-38BF-49D0-9F5A-DA0EB0A1CF21}" name="Chinese Grand Prix" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{1D828739-4FD5-40ED-A5B5-B23567BDE3FE}" name="Japanese Grand Prix" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{1062B4A0-6DF4-41F9-877D-4B43E48CCFE6}" name="Bahrain Grand Prix" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{1C734CE0-74E1-4F37-8C9E-9F2EE741BFE5}" name="Saudi Arabian Grand Prix" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{6DA07DD4-DD0E-4DB7-AEA7-F3A2E9225738}" name="Miami Grand Prix" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{257ED334-DEA1-4225-A408-3C2676795930}" name="Emilia Romagna Grand Prix" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{BAE89735-07AF-444C-B220-851C0CB3C754}" name="Monaco Grand Prix" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{B7D94A29-43B7-41DC-80C3-B1923F3E9284}" name="Spanish Grand Prix" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{21AA035A-318D-4FB7-BBBA-0C6D4F13E5CB}" name="Canadian Grand Prix" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{FACD5626-3EE1-4F7A-B7CB-6C80DE689297}" name="Austrian Grand Prix" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{D0953B36-F941-4B38-8251-D2477280E99D}" name="British Grand Prix" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{AC25F154-2768-4FDF-8473-44B8EF96F3F9}" name="Belgian Grand Prix" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{06BB5252-52C6-48F1-92DD-3677D94F6AD6}" name="Hungarian Grand Prix" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{6FCED645-DEDA-4065-8ED7-3401FF6E8A64}" name="Dutch Grand Prix" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{66976D97-649B-4E27-84FB-6BBBDE6B54DD}" name="Italian Grand Prix" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{41283C26-AE5C-4033-8465-C5C3B22E6094}" name="Azerbaijan Grand Prix" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{C4FE0C5A-0BCF-477D-ABC0-0A0D0583E97C}" name="Singapore Grand Prix" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{F69B7691-4E40-4AE7-846B-7BA48ADEE249}" name="United States Grand Prix" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{B7417A28-B404-40D9-AFF3-00A8B4A0C4D2}" name="Mexico City Grand Prix" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{FE4AA98D-B3DC-4364-BC04-FAE369D83855}" name="São Paulo Grand Prix" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{BCBF9F5E-E462-49BA-87E9-6620D01608A4}" name="Las Vegas Grand Prix" dataDxfId="4"/>
-    <tableColumn id="25" xr3:uid="{5963F622-6118-42F5-BD17-0A2B097489EC}" name="Qatar Grand Prix" dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{2B6C136A-A691-419C-9E4E-23006C9A0B32}" name="Abu Dhabi Grand Prix" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{F55A6B37-6EDE-41E4-B6B2-EE2FF245418C}" name="Australian Grand Prix" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{07D64B60-38BF-49D0-9F5A-DA0EB0A1CF21}" name="Chinese Grand Prix" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{1D828739-4FD5-40ED-A5B5-B23567BDE3FE}" name="Japanese Grand Prix" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{1062B4A0-6DF4-41F9-877D-4B43E48CCFE6}" name="Bahrain Grand Prix" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{1C734CE0-74E1-4F37-8C9E-9F2EE741BFE5}" name="Saudi Arabian Grand Prix" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{6DA07DD4-DD0E-4DB7-AEA7-F3A2E9225738}" name="Miami Grand Prix" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{257ED334-DEA1-4225-A408-3C2676795930}" name="Emilia Romagna Grand Prix" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{BAE89735-07AF-444C-B220-851C0CB3C754}" name="Monaco Grand Prix" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{B7D94A29-43B7-41DC-80C3-B1923F3E9284}" name="Spanish Grand Prix" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{21AA035A-318D-4FB7-BBBA-0C6D4F13E5CB}" name="Canadian Grand Prix" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{FACD5626-3EE1-4F7A-B7CB-6C80DE689297}" name="Austrian Grand Prix" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{D0953B36-F941-4B38-8251-D2477280E99D}" name="British Grand Prix" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{AC25F154-2768-4FDF-8473-44B8EF96F3F9}" name="Belgian Grand Prix" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{06BB5252-52C6-48F1-92DD-3677D94F6AD6}" name="Hungarian Grand Prix" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{6FCED645-DEDA-4065-8ED7-3401FF6E8A64}" name="Dutch Grand Prix" dataDxfId="16"/>
+    <tableColumn id="18" xr3:uid="{66976D97-649B-4E27-84FB-6BBBDE6B54DD}" name="Italian Grand Prix" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{41283C26-AE5C-4033-8465-C5C3B22E6094}" name="Azerbaijan Grand Prix" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{C4FE0C5A-0BCF-477D-ABC0-0A0D0583E97C}" name="Singapore Grand Prix" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{F69B7691-4E40-4AE7-846B-7BA48ADEE249}" name="United States Grand Prix" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{B7417A28-B404-40D9-AFF3-00A8B4A0C4D2}" name="Mexico City Grand Prix" dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{FE4AA98D-B3DC-4364-BC04-FAE369D83855}" name="São Paulo Grand Prix" dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{BCBF9F5E-E462-49BA-87E9-6620D01608A4}" name="Las Vegas Grand Prix" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{5963F622-6118-42F5-BD17-0A2B097489EC}" name="Qatar Grand Prix" dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{2B6C136A-A691-419C-9E4E-23006C9A0B32}" name="Abu Dhabi Grand Prix" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}" name="Table5" displayName="Table5" ref="A1:E21" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}" name="Table5" displayName="Table5" ref="A1:E21" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E21" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D9288ECF-7FB6-413D-B1F9-D0C1F542379A}" name="Team Name" dataDxfId="63">
+    <tableColumn id="1" xr3:uid="{D9288ECF-7FB6-413D-B1F9-D0C1F542379A}" name="Team Name" dataDxfId="4">
       <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$21,Drivers!$C$2:$C$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9F22078D-54A1-4A4A-AF23-B4137F60AB3E}" name="Constructor" dataDxfId="62">
+    <tableColumn id="2" xr3:uid="{9F22078D-54A1-4A4A-AF23-B4137F60AB3E}" name="Constructor" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$21,Drivers!$F$2:$F$21,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8E3FB958-7BB0-400F-A3F5-E8EC1EDBE678}" name="Driver" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{386A61E9-CDA2-4647-81AE-9E7EE26F203F}" name="Engine/Power Unit" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{FECB8E79-446F-4614-9058-29E64F3CE65C}" name="Chassis" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{8E3FB958-7BB0-400F-A3F5-E8EC1EDBE678}" name="Driver" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{386A61E9-CDA2-4647-81AE-9E7EE26F203F}" name="Engine/Power Unit" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{FECB8E79-446F-4614-9058-29E64F3CE65C}" name="Chassis" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5089,7 +3108,7 @@
       <c r="E3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="3">
         <v>5.2779999999999996</v>
       </c>
     </row>
@@ -5106,7 +3125,7 @@
       <c r="E4" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="3">
         <v>5.4509999999999996</v>
       </c>
     </row>
@@ -5123,7 +3142,7 @@
       <c r="E5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="3">
         <v>5.8070000000000004</v>
       </c>
     </row>
@@ -5140,7 +3159,7 @@
       <c r="E6" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="3">
         <v>5.4119999999999999</v>
       </c>
     </row>
@@ -5157,7 +3176,7 @@
       <c r="E7" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="3">
         <v>6.1740000000000004</v>
       </c>
     </row>
@@ -5174,7 +3193,7 @@
       <c r="E8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="3">
         <v>5.4119999999999999</v>
       </c>
     </row>
@@ -5191,7 +3210,7 @@
       <c r="E9" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="3">
         <v>4.9089999999999998</v>
       </c>
     </row>
@@ -5208,7 +3227,7 @@
       <c r="E10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="3">
         <v>3.3370000000000002</v>
       </c>
     </row>
@@ -5225,7 +3244,7 @@
       <c r="E11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="3">
         <v>4.6749999999999998</v>
       </c>
     </row>
@@ -5242,7 +3261,7 @@
       <c r="E12" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="3">
         <v>4.3609999999999998</v>
       </c>
     </row>
@@ -5259,7 +3278,7 @@
       <c r="E13" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="3">
         <v>4.3179999999999996</v>
       </c>
     </row>
@@ -5276,7 +3295,7 @@
       <c r="E14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="3">
         <v>5.891</v>
       </c>
     </row>
@@ -5293,7 +3312,7 @@
       <c r="E15" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="3">
         <v>7.0039999999999996</v>
       </c>
     </row>
@@ -5310,7 +3329,7 @@
       <c r="E16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="3">
         <v>4.3810000000000002</v>
       </c>
     </row>
@@ -5327,7 +3346,7 @@
       <c r="E17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="3">
         <v>4.2590000000000003</v>
       </c>
     </row>
@@ -5344,7 +3363,7 @@
       <c r="E18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="3">
         <v>5.7930000000000001</v>
       </c>
     </row>
@@ -5361,7 +3380,7 @@
       <c r="E19" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="3">
         <v>6.0030000000000001</v>
       </c>
     </row>
@@ -5378,7 +3397,7 @@
       <c r="E20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="3">
         <v>4.9279999999999999</v>
       </c>
     </row>
@@ -5395,7 +3414,7 @@
       <c r="E21" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="3">
         <v>5.5129999999999999</v>
       </c>
     </row>
@@ -5412,7 +3431,7 @@
       <c r="E22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="3">
         <v>4.3040000000000003</v>
       </c>
     </row>
@@ -5429,7 +3448,7 @@
       <c r="E23" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="3">
         <v>4.3090000000000002</v>
       </c>
     </row>
@@ -5446,7 +3465,7 @@
       <c r="E24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="3">
         <v>6.2009999999999996</v>
       </c>
     </row>
@@ -5463,7 +3482,7 @@
       <c r="E25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="3">
         <v>5.4189999999999996</v>
       </c>
     </row>
@@ -5480,7 +3499,7 @@
       <c r="E26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="3">
         <v>5.2809999999999997</v>
       </c>
     </row>
@@ -5722,7 +3741,7 @@
     <col min="28" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" ht="129" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="6" customFormat="1" ht="130.19999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -5879,73 +3898,57 @@
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="C3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="D3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="E3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="F3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="G3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="H3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="I3" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
-        <v/>
+      <c r="B3" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="C4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="D4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="E4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="F4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="G4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="H4" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>13</v>
+      <c r="B4" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="I4" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>17</v>
       </c>
     </row>
@@ -5953,36 +3956,28 @@
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="C5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="D5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="E5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="F5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="G5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="H5" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>10</v>
+      <c r="B5" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="I5" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>6</v>
       </c>
     </row>
@@ -5990,36 +3985,28 @@
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="C6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="D6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>20</v>
-      </c>
-      <c r="E6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="F6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="G6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="H6" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>16</v>
+      <c r="B6" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>179</v>
       </c>
       <c r="I6" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>19</v>
       </c>
     </row>
@@ -6027,36 +4014,28 @@
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="C7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="D7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="E7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="G7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>—5</v>
-      </c>
-      <c r="H7" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>—5</v>
+      <c r="B7" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>191</v>
       </c>
       <c r="I7" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>2</v>
       </c>
     </row>
@@ -6064,36 +4043,28 @@
       <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="C8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="D8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="E8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="F8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="G8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="H8" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>7</v>
+      <c r="B8" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="I8" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>7</v>
       </c>
     </row>
@@ -6101,36 +4072,28 @@
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="C9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="D9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="E9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="F9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="G9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="H9" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>12</v>
+      <c r="B9" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="I9" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>8</v>
       </c>
     </row>
@@ -6138,36 +4101,28 @@
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>PL</v>
-      </c>
-      <c r="C10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="D10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="E10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>20</v>
-      </c>
-      <c r="F10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="G10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="H10" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>19</v>
+      <c r="B10" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="I10" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>20</v>
       </c>
     </row>
@@ -6175,36 +4130,28 @@
       <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="C11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="D11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="E11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="F11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>20</v>
-      </c>
-      <c r="G11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="H11" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>18</v>
+      <c r="B11" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>188</v>
       </c>
       <c r="I11" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>16</v>
       </c>
     </row>
@@ -6212,36 +4159,28 @@
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="C12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>PL</v>
-      </c>
-      <c r="D12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="E12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="F12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="G12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="H12" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>11</v>
+      <c r="B12" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>186</v>
       </c>
       <c r="I12" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>13</v>
       </c>
     </row>
@@ -6249,36 +4188,28 @@
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="C13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="D13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="E13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="F13" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>10</v>
+      <c r="B13" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="G13" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
         <v>3</v>
       </c>
       <c r="H13" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
         <v>3</v>
       </c>
       <c r="I13" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>1</v>
       </c>
     </row>
@@ -6286,36 +4217,28 @@
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="C14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="D14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="E14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="F14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="H14" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>2</v>
+      <c r="B14" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="I14" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>3</v>
       </c>
     </row>
@@ -6323,36 +4246,28 @@
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="C15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="D15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="E15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="F15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="G15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H15" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>1</v>
+      <c r="B15" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="I15" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>15</v>
       </c>
     </row>
@@ -6360,36 +4275,28 @@
       <c r="A16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="C16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="D16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="E16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="F16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="G16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="H16" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>5</v>
+      <c r="B16" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>182</v>
       </c>
       <c r="I16" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>14</v>
       </c>
     </row>
@@ -6397,36 +4304,28 @@
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>—1</v>
-      </c>
-      <c r="C17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="D17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="E17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="F17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="G17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="H17" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>9</v>
+      <c r="B17" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="I17" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>5</v>
       </c>
     </row>
@@ -6434,36 +4333,28 @@
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="C18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="D18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="E18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="G18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>PL</v>
-      </c>
-      <c r="H18" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>PL</v>
+      <c r="B18" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="I18" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>12</v>
       </c>
     </row>
@@ -6471,36 +4362,28 @@
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="C19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="D19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="E19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="F19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="G19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="H19" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>4</v>
+      <c r="B19" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="I19" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>4</v>
       </c>
     </row>
@@ -6508,36 +4391,28 @@
       <c r="A20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>PL</v>
-      </c>
-      <c r="C20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="D20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="E20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="F20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="G20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="H20" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>14</v>
+      <c r="B20" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="I20" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>9</v>
       </c>
     </row>
@@ -6545,36 +4420,28 @@
       <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="C21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="D21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="E21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="F21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="G21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="H21" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>8</v>
+      <c r="B21" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>174</v>
       </c>
       <c r="I21" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>10</v>
       </c>
     </row>
@@ -6582,36 +4449,28 @@
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="C22" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="D22" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="E22" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="F22" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="G22" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="H22" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$P$24:$P$43,"")</f>
-        <v>15</v>
+      <c r="B22" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="I22" s="9">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$P$24:$P$43,"")</f>
         <v>11</v>
       </c>
     </row>
@@ -6693,740 +4552,580 @@
       <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="C25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>20</v>
-      </c>
-      <c r="D25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="E25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="F25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="G25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="H25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="I25" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v/>
+      <c r="B25" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="C26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="D26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="E26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="F26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="G26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="H26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="I26" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
+      <c r="B26" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="C27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="D27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="E27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="F27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="G27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="H27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="I27" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
+      <c r="B27" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="C28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="D28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>20</v>
-      </c>
-      <c r="E28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="F28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="G28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="H28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="I28" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>15</v>
+      <c r="B28" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="C29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="D29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="E29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="F29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="G29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>DNS5</v>
-      </c>
-      <c r="H29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>DNS5</v>
-      </c>
-      <c r="I29" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
+      <c r="B29" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="C30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="D30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="E30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="F30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="G30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="H30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I30" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
+      <c r="B30" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="C31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="D31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="E31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="F31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="G31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="H31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="I31" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
+      <c r="B31" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="C32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="D32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="E32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="G32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="H32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="I32" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
+      <c r="B32" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="C33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="D33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="E33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="F33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>18</v>
-      </c>
-      <c r="G33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="H33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
+      <c r="B33" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="C34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>19</v>
-      </c>
-      <c r="D34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="E34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>DSQ</v>
-      </c>
-      <c r="F34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>15</v>
-      </c>
-      <c r="G34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="H34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="I34" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>16</v>
+      <c r="B34" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="C35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="D35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="E35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="F35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="G35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="H35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I35" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
+      <c r="B35" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="C36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="D36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="E36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="F36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="G36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="H36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I36" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
+      <c r="B36" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="C37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="D37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="E37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="F37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="G37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="H37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>7</v>
-      </c>
-      <c r="I37" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>18</v>
+      <c r="B37" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="C38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="D38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="E38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="F38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="G38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="H38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
-      </c>
-      <c r="I38" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
+      <c r="B38" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>DNS1</v>
-      </c>
-      <c r="C39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="D39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="E39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="F39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="G39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="H39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
-      </c>
-      <c r="I39" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
+      <c r="B39" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="C40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="D40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="E40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="F40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="G40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="H40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="I40" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>17</v>
+      <c r="B40" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="C41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>3</v>
-      </c>
-      <c r="D41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>1</v>
-      </c>
-      <c r="E41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>6</v>
-      </c>
-      <c r="F41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>2</v>
-      </c>
-      <c r="G41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="H41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="I41" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>4</v>
+      <c r="B41" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="C42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="D42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="E42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>16</v>
-      </c>
-      <c r="F42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="G42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="H42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>13</v>
-      </c>
-      <c r="I42" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
+      <c r="B42" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>5</v>
-      </c>
-      <c r="C43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="D43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="E43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>12</v>
-      </c>
-      <c r="F43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
-      </c>
-      <c r="G43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="H43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>11</v>
-      </c>
-      <c r="I43" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>9</v>
+      <c r="B43" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Australian_Grand_Prix!$L$24:$L$43,[1]Australian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="C44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Chinese_Grand_Prix!$L$24:$L$43,[1]Chinese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>17</v>
-      </c>
-      <c r="D44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Japanese_Grand_Prix!$L$24:$L$43,[1]Japanese_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>14</v>
-      </c>
-      <c r="E44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Bahrain_Grand_Prix!$L$24:$L$43,[1]Bahrain_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="F44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Saudi_Arabian_Grand_Prix!$L$24:$L$43,[1]Saudi_Arabian_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>8</v>
-      </c>
-      <c r="G44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="H44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Miami_Grand_Prix!$L$24:$L$43,[1]Miami_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>Ret</v>
-      </c>
-      <c r="I44" s="9" t="str">
-        <f>_xlfn.XLOOKUP(Table4[[#This Row],[Driver]],[1]Monaco_Grand_Prix!$L$24:$L$43,[1]Monaco_Grand_Prix!$J$24:$J$43,"")</f>
-        <v>10</v>
+      <c r="B44" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -7448,7 +5147,7 @@
     <col min="4" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="13" customFormat="1" ht="129.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" s="13" customFormat="1" ht="130.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
@@ -7620,30 +5319,14 @@
         <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>BWT Alpine Formula One Team</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>174</v>
-      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -7657,30 +5340,14 @@
         <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>BWT Alpine Formula One Team</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="K4" s="23" t="s">
-        <v>182</v>
-      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
     </row>
     <row r="5" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -7694,30 +5361,14 @@
         <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Aston Martin Aramco Formula One Team</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>190</v>
-      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -7731,30 +5382,14 @@
         <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Aston Martin Aramco Formula One Team</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>198</v>
-      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
     </row>
     <row r="7" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
@@ -7768,30 +5403,14 @@
         <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Scuderia Ferrari HP</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>206</v>
-      </c>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -7805,30 +5424,14 @@
         <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Scuderia Ferrari HP</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>214</v>
-      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
     </row>
     <row r="9" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -7842,30 +5445,14 @@
         <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>MoneyGram Haas F1 Team</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>222</v>
-      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
     </row>
     <row r="10" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -7879,30 +5466,14 @@
         <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>MoneyGram Haas F1 Team</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>230</v>
-      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
@@ -7916,30 +5487,14 @@
         <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Stake F1 Team Kick Sauber</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>238</v>
-      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -7953,30 +5508,14 @@
         <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Stake F1 Team Kick Sauber</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="H12" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="K12" s="23" t="s">
-        <v>246</v>
-      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
     </row>
     <row r="13" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -7990,30 +5529,14 @@
         <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>McLaren Formula 1 Team</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="K13" s="23" t="s">
-        <v>254</v>
-      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
     </row>
     <row r="14" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
@@ -8027,30 +5550,14 @@
         <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>McLaren Formula 1 Team</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="J14" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="K14" s="23" t="s">
-        <v>262</v>
-      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
     </row>
     <row r="15" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -8064,30 +5571,14 @@
         <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Mercedes-AMG Petronas Formula One Team</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="H15" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="J15" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="K15" s="23" t="s">
-        <v>270</v>
-      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -8101,30 +5592,14 @@
         <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Mercedes-AMG Petronas Formula One Team</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="J16" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>278</v>
-      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
@@ -8138,30 +5613,14 @@
         <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Visa Cash App Racing Bulls Formula One Team</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="J17" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="K17" s="23" t="s">
-        <v>286</v>
-      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8175,30 +5634,14 @@
         <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Visa Cash App Racing Bulls Formula One Team</v>
       </c>
-      <c r="D18" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="J18" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>293</v>
-      </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
     </row>
     <row r="19" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
@@ -8212,30 +5655,14 @@
         <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Oracle Red Bull Racing</v>
       </c>
-      <c r="D19" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="K19" s="23" t="s">
-        <v>301</v>
-      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
     </row>
     <row r="20" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
@@ -8249,30 +5676,14 @@
         <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Oracle Red Bull Racing</v>
       </c>
-      <c r="D20" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="K20" s="23" t="s">
-        <v>309</v>
-      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
@@ -8286,30 +5697,14 @@
         <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Williams Racing</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="H21" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>317</v>
-      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
     </row>
     <row r="22" spans="1:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
@@ -8323,30 +5718,14 @@
         <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$21,Constructor!$A$2:$A$21,"")</f>
         <v>Williams Racing</v>
       </c>
-      <c r="D22" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="J22" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="K22" s="23" t="s">
-        <v>324</v>
-      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D24" s="16" t="s">
@@ -8703,7 +6082,7 @@
     <col min="28" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="129" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="130.19999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>9</v>
       </c>
